--- a/examples/reportes/memoria.xlsx
+++ b/examples/reportes/memoria.xlsx
@@ -503,7 +503,7 @@
     <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":209.06119791666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":204.900390625,"verticalRatio":0.3001945554748062,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":204.900390625,"verticalRatio":0.3001945554748062,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
   </si>
   <si>
-    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común, la NOM no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":364.71435546875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":218.49479166666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":214.333984375,"verticalRatio":0.31847671390503873,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común, la NOM no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":214.333984375,"verticalRatio":0.31847671390503873,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":218.49479166666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":214.333984375,"verticalRatio":0.31847671390503873,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":214.333984375,"verticalRatio":0.31847671390503873,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
   </si>
   <si>
     <t>{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","_margin":null,"_inlines":[],"_minWidth":53.4638671875,"_maxWidth":269.650390625,"listMarker":{"canvas":[{"x":41.166666666666664,"y":227.92838541666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":223.767578125,"verticalRatio":0.3367588723352713,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":223.767578125,"verticalRatio":0.3367588723352713,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
@@ -524,7 +524,7 @@
     <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":373.0904947916667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":368.9296875,"verticalRatio":0.6180807897286822,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":368.9296875,"verticalRatio":0.6180807897286822,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
   </si>
   <si>
-    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común, la NOM no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":364.71435546875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":382.5240885416667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":378.36328125,"verticalRatio":0.6363629481589147,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común, la NOM no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":378.36328125,"verticalRatio":0.6363629481589147,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":382.5240885416667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":378.36328125,"verticalRatio":0.6363629481589147,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":378.36328125,"verticalRatio":0.6363629481589147,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
   </si>
   <si>
     <t>{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","_margin":null,"_inlines":[],"_minWidth":53.4638671875,"_maxWidth":269.650390625,"listMarker":{"canvas":[{"x":41.166666666666664,"y":391.9576822916667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":387.796875,"verticalRatio":0.6546451065891473,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":387.796875,"verticalRatio":0.6546451065891473,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
@@ -542,7 +542,7 @@
     <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":522.5123697916666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":518.3515625,"verticalRatio":0.9076580668604651,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":518.3515625,"verticalRatio":0.9076580668604651,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
   </si>
   <si>
-    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común, la NOM no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":364.71435546875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":531.9459635416666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":527.78515625,"verticalRatio":0.9259402252906976,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común, la NOM no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":527.78515625,"verticalRatio":0.9259402252906976,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":531.9459635416666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":527.78515625,"verticalRatio":0.9259402252906976,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":527.78515625,"verticalRatio":0.9259402252906976,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
   </si>
   <si>
     <t>TAB-A — 220 V · 3F4H</t>
@@ -554,7 +554,7 @@
     <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":171.88932291666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":167.728515625,"verticalRatio":0.22815603803294573,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":167.728515625,"verticalRatio":0.22815603803294573,"horizontalRatio":0.010287509875351123},"pageNumbers":[5],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
   </si>
   <si>
-    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común, la NOM no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":364.71435546875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":181.32291666666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":177.162109375,"verticalRatio":0.2464381964631783,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común, la NOM no fija un valor).","startPosition":{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":177.162109375,"verticalRatio":0.2464381964631783,"horizontalRatio":0.010287509875351123},"pageNumbers":[5],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":181.32291666666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":177.162109375,"verticalRatio":0.2464381964631783,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":177.162109375,"verticalRatio":0.2464381964631783,"horizontalRatio":0.010287509875351123},"pageNumbers":[5],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
   </si>
   <si>
     <t>Elemento</t>
@@ -953,7 +953,7 @@
     <t>AL-1: Método nominal (cálculo a mano)</t>
   </si>
   <si>
-    <t>Caída de tensión (impedancia eficaz, Tabla 9 nota 2)</t>
+    <t>Caída de tensión (impedancia eficaz)</t>
   </si>
   <si>
     <t>ΔV = I · (R·cosφ + X·senφ) ;  %ΔV = ΔV / V_fn · 100</t>

--- a/examples/reportes/memoria.xlsx
+++ b/examples/reportes/memoria.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2823" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2823" uniqueCount="653">
   <si>
     <t>Memoria de cálculo</t>
   </si>
@@ -284,1105 +284,1120 @@
     <t>430-24 y 430-62(a)/430-63: alimentador de motores</t>
   </si>
   <si>
-    <t>2/0 AWG Cu</t>
+    <t>2/0 AWG (67.4 mm²) Cu</t>
+  </si>
+  <si>
+    <t>4 AWG (21.1 mm²)</t>
+  </si>
+  <si>
+    <t>calibre fijado</t>
+  </si>
+  <si>
+    <t>AL-2</t>
+  </si>
+  <si>
+    <t>INT-2</t>
+  </si>
+  <si>
+    <t>TR-2</t>
+  </si>
+  <si>
+    <t>450-3(b): protección del primario solamente</t>
+  </si>
+  <si>
+    <t>2 AWG (33.6 mm²) Cu</t>
+  </si>
+  <si>
+    <t>6 AWG (13.3 mm²)</t>
+  </si>
+  <si>
+    <t>AL-4</t>
+  </si>
+  <si>
+    <t>INT-4</t>
+  </si>
+  <si>
+    <t>TAB-B</t>
+  </si>
+  <si>
+    <t>215-2(a)(1) y 215-3</t>
+  </si>
+  <si>
+    <t>4 AWG (21.1 mm²) Cu</t>
+  </si>
+  <si>
+    <t>8 AWG (8.37 mm²)</t>
+  </si>
+  <si>
+    <t>AL-11</t>
+  </si>
+  <si>
+    <t>INT-11</t>
+  </si>
+  <si>
+    <t>M-01</t>
+  </si>
+  <si>
+    <t>derivado</t>
+  </si>
+  <si>
+    <t>430-52: protección del circuito derivado de motor</t>
+  </si>
+  <si>
+    <t>AL-12</t>
+  </si>
+  <si>
+    <t>INT-12</t>
+  </si>
+  <si>
+    <t>VFD-01</t>
+  </si>
+  <si>
+    <t>430-122(a): 125 % de la corriente de entrada del variador</t>
+  </si>
+  <si>
+    <t>8 AWG (8.37 mm²) Cu</t>
+  </si>
+  <si>
+    <t>10 AWG (5.26 mm²)</t>
+  </si>
+  <si>
+    <t>AL-13</t>
+  </si>
+  <si>
+    <t>INT-13</t>
+  </si>
+  <si>
+    <t>M-03</t>
+  </si>
+  <si>
+    <t>12 AWG (3.31 mm²) Cu</t>
+  </si>
+  <si>
+    <t>12 AWG (3.31 mm²)</t>
+  </si>
+  <si>
+    <t>AL-3</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>TAB-A</t>
+  </si>
+  <si>
+    <t>250 kcmil (127 mm²) Cu</t>
+  </si>
+  <si>
+    <t>AL-41</t>
+  </si>
+  <si>
+    <t>INT-41</t>
+  </si>
+  <si>
+    <t>L-02</t>
+  </si>
+  <si>
+    <t>210-19(a)(1) y 210-20(a)</t>
+  </si>
+  <si>
+    <t>AL-42</t>
+  </si>
+  <si>
+    <t>INT-42</t>
+  </si>
+  <si>
+    <t>CA-01</t>
+  </si>
+  <si>
+    <t>6 AWG (13.3 mm²) Cu</t>
+  </si>
+  <si>
+    <t>AL-21</t>
+  </si>
+  <si>
+    <t>INT-21</t>
+  </si>
+  <si>
+    <t>L-01</t>
+  </si>
+  <si>
+    <t>AL-22</t>
+  </si>
+  <si>
+    <t>INT-22</t>
+  </si>
+  <si>
+    <t>C-01</t>
+  </si>
+  <si>
+    <t>AL-23</t>
+  </si>
+  <si>
+    <t>INT-23</t>
+  </si>
+  <si>
+    <t>CG-01</t>
+  </si>
+  <si>
+    <t>TG — 480 V · 3F4H</t>
+  </si>
+  <si>
+    <t>Alimenta a</t>
+  </si>
+  <si>
+    <t>Fases</t>
+  </si>
+  <si>
+    <t>A (VA)</t>
+  </si>
+  <si>
+    <t>B (VA)</t>
+  </si>
+  <si>
+    <t>C (VA)</t>
+  </si>
+  <si>
+    <t>Total (VA)</t>
+  </si>
+  <si>
+    <t>P (kW)</t>
+  </si>
+  <si>
+    <t>Q (kvar)</t>
+  </si>
+  <si>
+    <t>I (A)</t>
+  </si>
+  <si>
+    <t>CCM-1, M-01, VFD-01, M-03</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>2/0 + 4 T</t>
+  </si>
+  <si>
+    <t>2 + 6 T</t>
+  </si>
+  <si>
+    <t>TAB-B, L-02, CA-01</t>
+  </si>
+  <si>
+    <t>4 + 8 T</t>
+  </si>
+  <si>
+    <t>Totales</t>
+  </si>
+  <si>
+    <t>Corriente por fase (A)</t>
+  </si>
+  <si>
+    <t>Desbalance (%)</t>
+  </si>
+  <si>
+    <t>límite 5 %</t>
+  </si>
+  <si>
+    <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":209.06119791666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":204.900390625,"verticalRatio":0.3001945554748062,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":204.900390625,"verticalRatio":0.3001945554748062,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+  </si>
+  <si>
+    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":218.49479166666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":214.333984375,"verticalRatio":0.31847671390503873,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":214.333984375,"verticalRatio":0.31847671390503873,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+  </si>
+  <si>
+    <t>{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","_margin":null,"_inlines":[],"_minWidth":53.4638671875,"_maxWidth":269.650390625,"listMarker":{"canvas":[{"x":41.166666666666664,"y":227.92838541666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":223.767578125,"verticalRatio":0.3367588723352713,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":223.767578125,"verticalRatio":0.3367588723352713,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+  </si>
+  <si>
+    <t>CCM-1 — 480 V · 3F4H</t>
+  </si>
+  <si>
+    <t>4 + 6 T</t>
+  </si>
+  <si>
+    <t>8 + 10 T</t>
+  </si>
+  <si>
+    <t>12 + 12 T</t>
+  </si>
+  <si>
+    <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":373.0904947916667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":368.9296875,"verticalRatio":0.6180807897286822,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":368.9296875,"verticalRatio":0.6180807897286822,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+  </si>
+  <si>
+    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":382.5240885416667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":378.36328125,"verticalRatio":0.6363629481589147,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":378.36328125,"verticalRatio":0.6363629481589147,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+  </si>
+  <si>
+    <t>{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","_margin":null,"_inlines":[],"_minWidth":53.4638671875,"_maxWidth":269.650390625,"listMarker":{"canvas":[{"x":41.166666666666664,"y":391.9576822916667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":387.796875,"verticalRatio":0.6546451065891473,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":387.796875,"verticalRatio":0.6546451065891473,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+  </si>
+  <si>
+    <t>TAB-B — 480 V · 3F4H</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>6 + 10 T</t>
+  </si>
+  <si>
+    <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":522.5123697916666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":518.3515625,"verticalRatio":0.9076580668604651,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":518.3515625,"verticalRatio":0.9076580668604651,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+  </si>
+  <si>
+    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":531.9459635416666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":527.78515625,"verticalRatio":0.9259402252906976,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":527.78515625,"verticalRatio":0.9259402252906976,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+  </si>
+  <si>
+    <t>TAB-A — 220 V · 3F4H</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":171.88932291666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":167.728515625,"verticalRatio":0.22815603803294573,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":167.728515625,"verticalRatio":0.22815603803294573,"horizontalRatio":0.010287509875351123},"pageNumbers":[5],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+  </si>
+  <si>
+    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":181.32291666666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":177.162109375,"verticalRatio":0.2464381964631783,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":177.162109375,"verticalRatio":0.2464381964631783,"horizontalRatio":0.010287509875351123},"pageNumbers":[5],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
+  </si>
+  <si>
+    <t>Elemento</t>
+  </si>
+  <si>
+    <t>Paso</t>
+  </si>
+  <si>
+    <t>Fórmula</t>
+  </si>
+  <si>
+    <t>Sustitución</t>
+  </si>
+  <si>
+    <t>Resultado</t>
+  </si>
+  <si>
+    <t>Referencias</t>
+  </si>
+  <si>
+    <t>ACOM-1</t>
+  </si>
+  <si>
+    <t>Red de suministro (acometida)</t>
+  </si>
+  <si>
+    <t>ACOM-1: fuente (Método nominal (cálculo a mano))</t>
+  </si>
+  <si>
+    <t>Tensión de la fuente</t>
+  </si>
+  <si>
+    <t>V = V_nom · pu</t>
+  </si>
+  <si>
+    <t>V = 23 000 · 1</t>
+  </si>
+  <si>
+    <t>23 000.0 V entre fases</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Impedancia de la red</t>
+  </si>
+  <si>
+    <t>No capturada: la fuente se considera ideal (tensión constante en su punto de conexión).</t>
+  </si>
+  <si>
+    <t>Potencia total suministrada</t>
+  </si>
+  <si>
+    <t>P = 136.894 kW ;  Q = 70.006 kvar ;  S = 153.755 kVA</t>
+  </si>
+  <si>
+    <t>Corriente suministrada</t>
+  </si>
+  <si>
+    <t>I = S / (√3 · V)</t>
+  </si>
+  <si>
+    <t>I = 153 755 / (√3 · 23 000)</t>
+  </si>
+  <si>
+    <t>3.86 A</t>
+  </si>
+  <si>
+    <t>TR-1</t>
+  </si>
+  <si>
+    <t>Transformador</t>
+  </si>
+  <si>
+    <t>TR-1: impedancia del transformador</t>
+  </si>
+  <si>
+    <t>Separación de %Z</t>
+  </si>
+  <si>
+    <t>%R = %Z / √(1 + (X/R)²) ;  %X = %R · X/R</t>
+  </si>
+  <si>
+    <t>%R = 5.75 / √(1 + 6²)</t>
+  </si>
+  <si>
+    <t>%R = 0.9453 % ;  %X = 5.6718 %</t>
+  </si>
+  <si>
+    <t>Impedancia base del secundario</t>
+  </si>
+  <si>
+    <t>Zb = V² / Sn</t>
+  </si>
+  <si>
+    <t>Zb = 480.0² / 750 000</t>
+  </si>
+  <si>
+    <t>0.30720 Ω</t>
+  </si>
+  <si>
+    <t>Impedancia referida al secundario</t>
+  </si>
+  <si>
+    <t>R = 0.00290 Ω ;  X = 0.01742 Ω</t>
+  </si>
+  <si>
+    <t>TR-1: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>Potencia aguas abajo</t>
+  </si>
+  <si>
+    <t>P = 136.894 kW ;  Q = 70.006 kvar ;  S = 153.755 kVA ;  FP = 0.8903</t>
+  </si>
+  <si>
+    <t>Corriente</t>
+  </si>
+  <si>
+    <t>I = 153 755.2 / (√3 · 480.0)</t>
+  </si>
+  <si>
+    <t>184.94 A</t>
+  </si>
+  <si>
+    <t>Corriente del primario</t>
+  </si>
+  <si>
+    <t>Regulación del transformador</t>
+  </si>
+  <si>
+    <t>%ΔV ≈ (S / Sn) · (%R · cosφ + %X · senφ)</t>
+  </si>
+  <si>
+    <t>%ΔV = (153 755 / 750 000) · (0.9453 · 0.8903 + 5.6718 · 0.4553)</t>
+  </si>
+  <si>
+    <t>0.702 %</t>
+  </si>
+  <si>
+    <t>Tablero</t>
+  </si>
+  <si>
+    <t>TG: tensión en barras</t>
+  </si>
+  <si>
+    <t>Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>476.6 V (99.30 % de 480 V)</t>
+  </si>
+  <si>
+    <t>Interruptor / protección</t>
+  </si>
+  <si>
+    <t>Selección de la protección</t>
+  </si>
+  <si>
+    <t>Corriente de diseño del alimentador (430-24)</t>
+  </si>
+  <si>
+    <t>I_d = 1.25 · I_mayor + Σ I_otros motores + I_no continua + 1.25 · I_continua</t>
+  </si>
+  <si>
+    <t>I_d = 1.25 · 65.00 (M-01) + 45.36 + 0.00 + 1.25 · 0.00</t>
+  </si>
+  <si>
+    <t>126.61 A</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 430-24</t>
+  </si>
+  <si>
+    <t>Protección máxima del alimentador (430-62(a), 430-63)</t>
+  </si>
+  <si>
+    <t>I_prot ≤ mayor protección de derivado + Σ demás corrientes de motores + otras cargas</t>
+  </si>
+  <si>
+    <t>175 A (AL-11) + 45.36 + 0.00 = 220.36 A</t>
+  </si>
+  <si>
+    <t>200 A (valor estándar no mayor)</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 430-62(a) · 430-63 · 240-6(a)</t>
+  </si>
+  <si>
+    <t>INT-1: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>P = 80.598 kW ;  Q = 42.740 kvar ;  S = 91.229 kVA ;  FP = 0.8835</t>
+  </si>
+  <si>
+    <t>I = 91 228.8 / (√3 · 480.0)</t>
+  </si>
+  <si>
+    <t>109.73 A</t>
+  </si>
+  <si>
+    <t>Caída de tensión</t>
+  </si>
+  <si>
+    <t>Sin impedancia (0 %)</t>
+  </si>
+  <si>
+    <t>Corriente nominal del primario</t>
+  </si>
+  <si>
+    <t>I = Sn / (√3 · V)</t>
+  </si>
+  <si>
+    <t>I = 75 000 / (√3 · 480)</t>
+  </si>
+  <si>
+    <t>90.21 A</t>
+  </si>
+  <si>
+    <t>Protección máxima del primario</t>
+  </si>
+  <si>
+    <t>I_prot ≤ 125 % · I_pri (si no es estándar, el inmediato superior: Tabla 450-3(b) nota 1)</t>
+  </si>
+  <si>
+    <t>1.25 · 90.21 = 112.76 A</t>
+  </si>
+  <si>
+    <t>125 A</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 Tabla 450-3(b) · 240-6(a)</t>
+  </si>
+  <si>
+    <t>INT-2: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>P = 17.296 kW ;  Q = 8.377 kvar ;  S = 19.218 kVA ;  FP = 0.9000</t>
+  </si>
+  <si>
+    <t>I = 19 217.8 / (√3 · 480.0)</t>
+  </si>
+  <si>
+    <t>23.12 A</t>
+  </si>
+  <si>
+    <t>L-02: corriente</t>
+  </si>
+  <si>
+    <t>4.01 A — continua (alumbrado: continua por defecto)</t>
+  </si>
+  <si>
+    <t>CA-01: corriente</t>
+  </si>
+  <si>
+    <t>48.11 A — no continua (no continua por defecto)</t>
+  </si>
+  <si>
+    <t>Corriente de diseño</t>
+  </si>
+  <si>
+    <t>I_d = I_no continua + 1.25 · I_continua</t>
+  </si>
+  <si>
+    <t>I_d = 48.11 + 1.25 · 4.01</t>
+  </si>
+  <si>
+    <t>53.12 A</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 215-2(a)(1)</t>
+  </si>
+  <si>
+    <t>I_prot ≥ I_d (valor estándar inmediato)</t>
+  </si>
+  <si>
+    <t>60 A</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 215-3 · 240-6(a)</t>
+  </si>
+  <si>
+    <t>INT-4: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>P = 39.000 kW ;  Q = 18.889 kvar ;  S = 43.333 kVA ;  FP = 0.9000</t>
+  </si>
+  <si>
+    <t>I = 43 333.3 / (√3 · 480.0)</t>
+  </si>
+  <si>
+    <t>52.12 A</t>
+  </si>
+  <si>
+    <t>Alimentador (cable)</t>
+  </si>
+  <si>
+    <t>Dimensionamiento</t>
+  </si>
+  <si>
+    <t>Temperatura nominal del conductor</t>
+  </si>
+  <si>
+    <t>THHW-LS: 75 °C lugares mojados; 90 °C lugares secos</t>
+  </si>
+  <si>
+    <t>90 °C</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 Tabla 310-104(a) · Se toma la mayor temperatura del aislamiento; en lugares mojados aplica la indicada para ellos.</t>
+  </si>
+  <si>
+    <t>Temperatura de terminales</t>
+  </si>
+  <si>
+    <t>circuito de 200 A &gt; 100 A (110-14(c)(1)(b))</t>
+  </si>
+  <si>
+    <t>75 °C</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 110-14(c)</t>
+  </si>
+  <si>
+    <t>Factor de corrección por temperatura ambiente</t>
+  </si>
+  <si>
+    <t>30 °C (temperatura ambiente del proyecto), columna de 90 °C</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 Tabla 310-15(b)(2)(a)</t>
+  </si>
+  <si>
+    <t>Factor de ajuste por agrupamiento</t>
+  </si>
+  <si>
+    <t>3 conductores portadores de corriente en la canalización</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 Tabla 310-15(b)(3)(a)</t>
+  </si>
+  <si>
+    <t>Verificación del calibre fijado</t>
+  </si>
+  <si>
+    <t>2/0 AWG: 90 °C → 195 A · 1 · 1 = 195.00 A ; terminales 75 °C: 175.00 A ; ampacidad = 175.00 A</t>
+  </si>
+  <si>
+    <t>Cumple ampacidad y protección</t>
+  </si>
+  <si>
+    <t>Caída de tensión con el calibre elegido</t>
+  </si>
+  <si>
+    <t>0.593 % ≤ 3 % (NOM-001-SEDE-2012 215-2(a)(1) Nota 2 (recomendación))</t>
+  </si>
+  <si>
+    <t>Conductor de puesta a tierra de equipos</t>
+  </si>
+  <si>
+    <t>200 A → 6 AWG Cu (13.3 mm²) ; aumento proporcional (250-122(b)): 13.30 · 67.43 / 42.41 = 21.15 mm² → 4</t>
   </si>
   <si>
     <t>4 AWG</t>
   </si>
   <si>
-    <t>calibre fijado</t>
-  </si>
-  <si>
-    <t>AL-2</t>
-  </si>
-  <si>
-    <t>INT-2</t>
-  </si>
-  <si>
-    <t>TR-2</t>
-  </si>
-  <si>
-    <t>450-3(b): protección del primario solamente</t>
-  </si>
-  <si>
-    <t>2 AWG Cu</t>
+    <t>NOM-001-SEDE-2012 Tabla 250-122</t>
+  </si>
+  <si>
+    <t>AL-1: impedancia del conductor</t>
+  </si>
+  <si>
+    <t>Resistencia y reactancia por conductor</t>
+  </si>
+  <si>
+    <t>2/0 Cu, conduit de acero, 75 °C</t>
+  </si>
+  <si>
+    <t>R = 0.33 Ω/km ;  XL = 0.177 Ω/km</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 Capítulo 10, Tabla 9</t>
+  </si>
+  <si>
+    <t>Impedancia del tramo</t>
+  </si>
+  <si>
+    <t>Z = (R + jXL) · L / n</t>
+  </si>
+  <si>
+    <t>Z = (0.33 + j0.177) · 0.0400 km / 1</t>
+  </si>
+  <si>
+    <t>R = 0.01320 Ω ;  X = 0.00708 Ω</t>
+  </si>
+  <si>
+    <t>AL-1: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>Caída de tensión (impedancia eficaz)</t>
+  </si>
+  <si>
+    <t>ΔV = I · (R·cosφ + X·senφ) ;  %ΔV = ΔV / V_fn · 100</t>
+  </si>
+  <si>
+    <t>ΔV = 109.73 · (0.01320 · 0.8835 + 0.00708 · 0.4685) = 1.644 V ;  %ΔV = 1.644 / 277.13 · 100</t>
+  </si>
+  <si>
+    <t>0.593 %</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 Capítulo 10, Tabla 9, nota 2</t>
+  </si>
+  <si>
+    <t>Centro de control de motores (CCM)</t>
+  </si>
+  <si>
+    <t>CCM-1: tensión en barras</t>
+  </si>
+  <si>
+    <t>473.8 V (98.70 % de 480 V)</t>
+  </si>
+  <si>
+    <t>circuito de 125 A &gt; 100 A (110-14(c)(1)(b))</t>
+  </si>
+  <si>
+    <t>2 AWG: 90 °C → 130 A · 1 · 1 = 130.00 A ; terminales 75 °C: 115.00 A ; ampacidad = 115.00 A</t>
+  </si>
+  <si>
+    <t>0.113 % ≤ 3 % (NOM-001-SEDE-2012 215-2(a)(1) Nota 2 (recomendación))</t>
+  </si>
+  <si>
+    <t>125 A → 6 AWG Cu (13.3 mm²)</t>
   </si>
   <si>
     <t>6 AWG</t>
   </si>
   <si>
-    <t>AL-4</t>
-  </si>
-  <si>
-    <t>INT-4</t>
-  </si>
-  <si>
-    <t>TAB-B</t>
-  </si>
-  <si>
-    <t>215-2(a)(1) y 215-3</t>
-  </si>
-  <si>
-    <t>4 AWG Cu</t>
+    <t>AL-2: impedancia del conductor</t>
+  </si>
+  <si>
+    <t>2 Cu, conduit de acero, 75 °C</t>
+  </si>
+  <si>
+    <t>R = 0.66 Ω/km ;  XL = 0.187 Ω/km</t>
+  </si>
+  <si>
+    <t>Z = (0.66 + j0.187) · 0.0200 km / 1</t>
+  </si>
+  <si>
+    <t>R = 0.01320 Ω ;  X = 0.00374 Ω</t>
+  </si>
+  <si>
+    <t>AL-2: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>ΔV = 23.12 · (0.01320 · 0.9000 + 0.00374 · 0.4359) = 0.312 V ;  %ΔV = 0.312 / 277.13 · 100</t>
+  </si>
+  <si>
+    <t>0.113 %</t>
+  </si>
+  <si>
+    <t>circuito de 60 A ≤ 100 A (110-14(c)(1)(a))</t>
+  </si>
+  <si>
+    <t>60 °C</t>
+  </si>
+  <si>
+    <t>4 AWG: 90 °C → 95 A · 1 · 1 = 95.00 A ; terminales 60 °C: 70.00 A ; ampacidad = 70.00 A</t>
+  </si>
+  <si>
+    <t>0.928 % ≤ 3 % (NOM-001-SEDE-2012 215-2(a)(1) Nota 2 (recomendación))</t>
+  </si>
+  <si>
+    <t>60 A → 10 AWG Cu (5.26 mm²) ; aumento proporcional (250-122(b)): 5.26 · 21.15 / 13.30 = 8.36 mm² → 8</t>
   </si>
   <si>
     <t>8 AWG</t>
   </si>
   <si>
-    <t>AL-11</t>
-  </si>
-  <si>
-    <t>INT-11</t>
-  </si>
-  <si>
-    <t>M-01</t>
-  </si>
-  <si>
-    <t>derivado</t>
-  </si>
-  <si>
-    <t>430-52: protección del circuito derivado de motor</t>
-  </si>
-  <si>
-    <t>AL-12</t>
-  </si>
-  <si>
-    <t>INT-12</t>
-  </si>
-  <si>
-    <t>VFD-01</t>
-  </si>
-  <si>
-    <t>430-122(a): 125 % de la corriente de entrada del variador</t>
-  </si>
-  <si>
-    <t>8 AWG Cu</t>
+    <t>AL-4: impedancia del conductor</t>
+  </si>
+  <si>
+    <t>4 Cu, conduit de PVC, 75 °C</t>
+  </si>
+  <si>
+    <t>R = 1.02 Ω/km ;  XL = 0.157 Ω/km</t>
+  </si>
+  <si>
+    <t>Z = (1.02 + j0.157) · 0.0500 km / 1</t>
+  </si>
+  <si>
+    <t>R = 0.05100 Ω ;  X = 0.00785 Ω</t>
+  </si>
+  <si>
+    <t>AL-4: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>ΔV = 52.12 · (0.05100 · 0.9000 + 0.00785 · 0.4359) = 2.571 V ;  %ΔV = 2.571 / 277.13 · 100</t>
+  </si>
+  <si>
+    <t>0.928 %</t>
+  </si>
+  <si>
+    <t>TAB-B: tensión en barras</t>
+  </si>
+  <si>
+    <t>472.2 V (98.37 % de 480 V)</t>
+  </si>
+  <si>
+    <t>Corriente de diseño del conductor</t>
+  </si>
+  <si>
+    <t>I_d = 1.25 · I</t>
+  </si>
+  <si>
+    <t>I_d = 1.25 · 65.00 (corriente de tabla)</t>
+  </si>
+  <si>
+    <t>81.25 A</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 430-22</t>
+  </si>
+  <si>
+    <t>Protección contra cortocircuito y falla a tierra</t>
+  </si>
+  <si>
+    <t>I_prot ≤ 250 % · I_pc ; si no es estándar, el inmediato superior (430-52(c)(1) Exc. 1)</t>
+  </si>
+  <si>
+    <t>2.5 · 65.00 = 162.50 A (Interruptor automático de tiempo inverso², De jaula de ardilla: diferentes de los de diseño B energéticamente eficientes)</t>
+  </si>
+  <si>
+    <t>175 A</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 Tabla 430-52 · 240-6(a)</t>
+  </si>
+  <si>
+    <t>INT-11: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>P = 45.934 kW ;  Q = 28.467 kvar ;  S = 54.040 kVA ;  FP = 0.8500</t>
+  </si>
+  <si>
+    <t>I = 54 040.0 / (√3 · 480.0)</t>
+  </si>
+  <si>
+    <t>65.00 A</t>
+  </si>
+  <si>
+    <t>I_d = 1.25 · I_ent</t>
+  </si>
+  <si>
+    <t>I_d = 1.25 · 31.36 (corriente de entrada calculada con la carga (no se capturó la de placa))</t>
+  </si>
+  <si>
+    <t>39.20 A</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 430-122(a)</t>
+  </si>
+  <si>
+    <t>Protección propuesta</t>
+  </si>
+  <si>
+    <t>40 A</t>
+  </si>
+  <si>
+    <t>Valor estándar ≥ corriente de diseño (240-6(a)). Confirmar con las instrucciones del fabricante del variador (430-130).</t>
+  </si>
+  <si>
+    <t>INT-12: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>P = 24.770 kW ;  Q = 8.142 kvar ;  S = 26.074 kVA ;  FP = 0.9500</t>
+  </si>
+  <si>
+    <t>I = 26 073.8 / (√3 · 480.0)</t>
+  </si>
+  <si>
+    <t>31.36 A</t>
+  </si>
+  <si>
+    <t>I_d = 1.25 · 14.00 (corriente de tabla)</t>
+  </si>
+  <si>
+    <t>17.50 A</t>
+  </si>
+  <si>
+    <t>2.5 · 14.00 = 35.00 A (Interruptor automático de tiempo inverso², De jaula de ardilla: diferentes de los de diseño B energéticamente eficientes)</t>
+  </si>
+  <si>
+    <t>35 A</t>
+  </si>
+  <si>
+    <t>INT-13: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>P = 9.893 kW ;  Q = 6.131 kvar ;  S = 11.639 kVA ;  FP = 0.8500</t>
+  </si>
+  <si>
+    <t>I = 11 639.4 / (√3 · 480.0)</t>
+  </si>
+  <si>
+    <t>14.00 A</t>
+  </si>
+  <si>
+    <t>TR-2: impedancia del transformador</t>
+  </si>
+  <si>
+    <t>%R = 4 / √(1 + 2²)</t>
+  </si>
+  <si>
+    <t>%R = 1.7889 % ;  %X = 3.5777 %</t>
+  </si>
+  <si>
+    <t>Zb = 220.0² / 75 000</t>
+  </si>
+  <si>
+    <t>0.64533 Ω</t>
+  </si>
+  <si>
+    <t>R = 0.01154 Ω ;  X = 0.02309 Ω</t>
+  </si>
+  <si>
+    <t>TR-2: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>I = 19 217.8 / (√3 · 220.0)</t>
+  </si>
+  <si>
+    <t>50.43 A</t>
+  </si>
+  <si>
+    <t>%ΔV = (19 218 / 75 000) · (1.7889 · 0.9000 + 3.5777 · 0.4359)</t>
+  </si>
+  <si>
+    <t>0.812 %</t>
+  </si>
+  <si>
+    <t>12.03 A — continua (alumbrado: continua por defecto)</t>
+  </si>
+  <si>
+    <t>I_d = 0.00 + 1.25 · 12.03</t>
+  </si>
+  <si>
+    <t>15.04 A</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 210-19(a)(1)</t>
+  </si>
+  <si>
+    <t>16 A</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 210-20(a) · 240-6(a)</t>
+  </si>
+  <si>
+    <t>INT-41: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>P = 3.000 kW ;  Q = 1.453 kvar ;  S = 3.333 kVA ;  FP = 0.9000</t>
+  </si>
+  <si>
+    <t>I = S / V</t>
+  </si>
+  <si>
+    <t>I = 3 333.3 / 277.1</t>
+  </si>
+  <si>
+    <t>12.03 A</t>
+  </si>
+  <si>
+    <t>I_d = 48.11 + 1.25 · 0.00</t>
+  </si>
+  <si>
+    <t>48.11 A</t>
+  </si>
+  <si>
+    <t>50 A</t>
+  </si>
+  <si>
+    <t>INT-42: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>P = 36.000 kW ;  Q = 17.436 kvar ;  S = 40.000 kVA ;  FP = 0.9000</t>
+  </si>
+  <si>
+    <t>I = 40 000.0 / (√3 · 480.0)</t>
+  </si>
+  <si>
+    <t>motor con letra de diseño B: se permiten 75 °C (110-14(c)(1)(a)(4))</t>
+  </si>
+  <si>
+    <t>4 AWG: 90 °C → 95 A · 1 · 1 = 95.00 A ; terminales 75 °C: 85.00 A ; ampacidad = 85.00 A</t>
+  </si>
+  <si>
+    <t>0.569 % ≤ 3 % (NOM-001-SEDE-2012 210-19(a) Nota 4 (recomendación))</t>
+  </si>
+  <si>
+    <t>175 A → 6 AWG Cu (13.3 mm²)</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 Tabla 250-122 · 250-122(d)(1)</t>
+  </si>
+  <si>
+    <t>AL-11: impedancia del conductor</t>
+  </si>
+  <si>
+    <t>4 Cu, conduit de acero, 75 °C</t>
+  </si>
+  <si>
+    <t>R = 1.02 Ω/km ;  XL = 0.197 Ω/km</t>
+  </si>
+  <si>
+    <t>Z = (1.02 + j0.197) · 0.0250 km / 1</t>
+  </si>
+  <si>
+    <t>R = 0.02550 Ω ;  X = 0.00493 Ω</t>
+  </si>
+  <si>
+    <t>AL-11: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>ΔV = 65.00 · (0.02550 · 0.8500 + 0.00493 · 0.5268) = 1.578 V ;  %ΔV = 1.578 / 277.13 · 100</t>
+  </si>
+  <si>
+    <t>0.569 %</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>M-01: potencia demandada</t>
+  </si>
+  <si>
+    <t>Corriente a plena carga del motor (tabla)</t>
+  </si>
+  <si>
+    <t>50 hp, trifásico, columna de 460 V</t>
+  </si>
+  <si>
+    <t>65.0 A</t>
+  </si>
+  <si>
+    <t>NOM-001-SEDE-2012 Tabla 430-250 · 430-6(a)(1)</t>
+  </si>
+  <si>
+    <t>Potencia aparente a la tensión nominal del sistema</t>
+  </si>
+  <si>
+    <t>S = √3 · V_sis · I</t>
+  </si>
+  <si>
+    <t>S = √3 · 480 · 65.0</t>
+  </si>
+  <si>
+    <t>54.040 kVA</t>
+  </si>
+  <si>
+    <t>Potencias activa y reactiva</t>
+  </si>
+  <si>
+    <t>P = S · FP ;  Q = S · sen(arccos FP)</t>
+  </si>
+  <si>
+    <t>P = 54 040.0 · 0.85 ;  Q = 54 040.0 · 0.5268</t>
+  </si>
+  <si>
+    <t>P = 45.934 kW ;  Q = 28.467 kvar</t>
+  </si>
+  <si>
+    <t>M-01: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>Corriente de la carga</t>
+  </si>
+  <si>
+    <t>Tensión en terminales</t>
+  </si>
+  <si>
+    <t>471.1 V (98.14 % de 480.0 V entre fases)</t>
+  </si>
+  <si>
+    <t>Caída acumulada en conductores desde el origen de la zona</t>
+  </si>
+  <si>
+    <t>1.162 %</t>
+  </si>
+  <si>
+    <t>circuito de 40 A ≤ 100 A (110-14(c)(1)(a))</t>
+  </si>
+  <si>
+    <t>8 AWG: 90 °C → 55 A · 1 · 1 = 55.00 A ; terminales 60 °C: 40.00 A ; ampacidad = 40.00 A</t>
+  </si>
+  <si>
+    <t>0.848 % ≤ 3 % (NOM-001-SEDE-2012 210-19(a) Nota 4 (recomendación))</t>
+  </si>
+  <si>
+    <t>40 A → 10 AWG Cu (5.26 mm²)</t>
   </si>
   <si>
     <t>10 AWG</t>
   </si>
   <si>
-    <t>AL-13</t>
-  </si>
-  <si>
-    <t>INT-13</t>
-  </si>
-  <si>
-    <t>M-03</t>
-  </si>
-  <si>
-    <t>12 AWG Cu</t>
+    <t>AL-12: impedancia del conductor</t>
+  </si>
+  <si>
+    <t>8 Cu, conduit de acero, 75 °C</t>
+  </si>
+  <si>
+    <t>R = 2.56 Ω/km ;  XL = 0.213 Ω/km</t>
+  </si>
+  <si>
+    <t>Z = (2.56 + j0.213) · 0.0300 km / 1</t>
+  </si>
+  <si>
+    <t>R = 0.07680 Ω ;  X = 0.00639 Ω</t>
+  </si>
+  <si>
+    <t>AL-12: Método nominal (cálculo a mano)</t>
+  </si>
+  <si>
+    <t>ΔV = 31.36 · (0.07680 · 0.9500 + 0.00639 · 0.3122) = 2.351 V ;  %ΔV = 2.351 / 277.13 · 100</t>
+  </si>
+  <si>
+    <t>0.848 %</t>
+  </si>
+  <si>
+    <t>12 AWG: 90 °C → 30 A · 1 · 1 = 30.00 A ; terminales 75 °C: 25.00 A ; ampacidad = 25.00 A</t>
+  </si>
+  <si>
+    <t>0.868 % ≤ 3 % (NOM-001-SEDE-2012 210-19(a) Nota 4 (recomendación))</t>
+  </si>
+  <si>
+    <t>35 A → 10 AWG Cu (5.26 mm²) ; aumento proporcional (250-122(b)): 5.26 · 3.31 / 2.08 = 8.37 mm² → 6 ; no se exige mayor que la fase (250-122(a)) → 12</t>
   </si>
   <si>
     <t>12 AWG</t>
-  </si>
-  <si>
-    <t>AL-3</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>TAB-A</t>
-  </si>
-  <si>
-    <t>250 kcmil Cu</t>
-  </si>
-  <si>
-    <t>AL-41</t>
-  </si>
-  <si>
-    <t>INT-41</t>
-  </si>
-  <si>
-    <t>L-02</t>
-  </si>
-  <si>
-    <t>210-19(a)(1) y 210-20(a)</t>
-  </si>
-  <si>
-    <t>AL-42</t>
-  </si>
-  <si>
-    <t>INT-42</t>
-  </si>
-  <si>
-    <t>CA-01</t>
-  </si>
-  <si>
-    <t>6 AWG Cu</t>
-  </si>
-  <si>
-    <t>AL-21</t>
-  </si>
-  <si>
-    <t>INT-21</t>
-  </si>
-  <si>
-    <t>L-01</t>
-  </si>
-  <si>
-    <t>AL-22</t>
-  </si>
-  <si>
-    <t>INT-22</t>
-  </si>
-  <si>
-    <t>C-01</t>
-  </si>
-  <si>
-    <t>AL-23</t>
-  </si>
-  <si>
-    <t>INT-23</t>
-  </si>
-  <si>
-    <t>CG-01</t>
-  </si>
-  <si>
-    <t>TG — 480 V · 3F4H</t>
-  </si>
-  <si>
-    <t>Alimenta a</t>
-  </si>
-  <si>
-    <t>Fases</t>
-  </si>
-  <si>
-    <t>A (VA)</t>
-  </si>
-  <si>
-    <t>B (VA)</t>
-  </si>
-  <si>
-    <t>C (VA)</t>
-  </si>
-  <si>
-    <t>Total (VA)</t>
-  </si>
-  <si>
-    <t>P (kW)</t>
-  </si>
-  <si>
-    <t>Q (kvar)</t>
-  </si>
-  <si>
-    <t>I (A)</t>
-  </si>
-  <si>
-    <t>CCM-1, M-01, VFD-01, M-03</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>2/0 + 4 T</t>
-  </si>
-  <si>
-    <t>2 + 6 T</t>
-  </si>
-  <si>
-    <t>TAB-B, L-02, CA-01</t>
-  </si>
-  <si>
-    <t>4 + 8 T</t>
-  </si>
-  <si>
-    <t>Totales</t>
-  </si>
-  <si>
-    <t>Corriente por fase (A)</t>
-  </si>
-  <si>
-    <t>Desbalance (%)</t>
-  </si>
-  <si>
-    <t>límite 5 %</t>
-  </si>
-  <si>
-    <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":209.06119791666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":204.900390625,"verticalRatio":0.3001945554748062,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":204.900390625,"verticalRatio":0.3001945554748062,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
-  </si>
-  <si>
-    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":218.49479166666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":214.333984375,"verticalRatio":0.31847671390503873,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":214.333984375,"verticalRatio":0.31847671390503873,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
-  </si>
-  <si>
-    <t>{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","_margin":null,"_inlines":[],"_minWidth":53.4638671875,"_maxWidth":269.650390625,"listMarker":{"canvas":[{"x":41.166666666666664,"y":227.92838541666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":223.767578125,"verticalRatio":0.3367588723352713,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":223.767578125,"verticalRatio":0.3367588723352713,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
-  </si>
-  <si>
-    <t>CCM-1 — 480 V · 3F4H</t>
-  </si>
-  <si>
-    <t>4 + 6 T</t>
-  </si>
-  <si>
-    <t>8 + 10 T</t>
-  </si>
-  <si>
-    <t>12 + 12 T</t>
-  </si>
-  <si>
-    <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":373.0904947916667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":368.9296875,"verticalRatio":0.6180807897286822,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":368.9296875,"verticalRatio":0.6180807897286822,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
-  </si>
-  <si>
-    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":382.5240885416667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":378.36328125,"verticalRatio":0.6363629481589147,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":378.36328125,"verticalRatio":0.6363629481589147,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
-  </si>
-  <si>
-    <t>{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","_margin":null,"_inlines":[],"_minWidth":53.4638671875,"_maxWidth":269.650390625,"listMarker":{"canvas":[{"x":41.166666666666664,"y":391.9576822916667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":387.796875,"verticalRatio":0.6546451065891473,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":387.796875,"verticalRatio":0.6546451065891473,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
-  </si>
-  <si>
-    <t>TAB-B — 480 V · 3F4H</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>6 + 10 T</t>
-  </si>
-  <si>
-    <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":522.5123697916666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":518.3515625,"verticalRatio":0.9076580668604651,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":518.3515625,"verticalRatio":0.9076580668604651,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
-  </si>
-  <si>
-    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":531.9459635416666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":527.78515625,"verticalRatio":0.9259402252906976,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":527.78515625,"verticalRatio":0.9259402252906976,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
-  </si>
-  <si>
-    <t>TAB-A — 220 V · 3F4H</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":171.88932291666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":167.728515625,"verticalRatio":0.22815603803294573,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":167.728515625,"verticalRatio":0.22815603803294573,"horizontalRatio":0.010287509875351123},"pageNumbers":[5],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
-  </si>
-  <si>
-    <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":181.32291666666666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":177.162109375,"verticalRatio":0.2464381964631783,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":177.162109375,"verticalRatio":0.2464381964631783,"horizontalRatio":0.010287509875351123},"pageNumbers":[5],"pages":38,"stack":false},"pageBreakCalculated":true}</t>
-  </si>
-  <si>
-    <t>Elemento</t>
-  </si>
-  <si>
-    <t>Paso</t>
-  </si>
-  <si>
-    <t>Fórmula</t>
-  </si>
-  <si>
-    <t>Sustitución</t>
-  </si>
-  <si>
-    <t>Resultado</t>
-  </si>
-  <si>
-    <t>Referencias</t>
-  </si>
-  <si>
-    <t>ACOM-1</t>
-  </si>
-  <si>
-    <t>Red de suministro (acometida)</t>
-  </si>
-  <si>
-    <t>ACOM-1: fuente (Método nominal (cálculo a mano))</t>
-  </si>
-  <si>
-    <t>Tensión de la fuente</t>
-  </si>
-  <si>
-    <t>V = V_nom · pu</t>
-  </si>
-  <si>
-    <t>V = 23 000 · 1</t>
-  </si>
-  <si>
-    <t>23 000.0 V entre fases</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Impedancia de la red</t>
-  </si>
-  <si>
-    <t>No capturada: la fuente se considera ideal (tensión constante en su punto de conexión).</t>
-  </si>
-  <si>
-    <t>Potencia total suministrada</t>
-  </si>
-  <si>
-    <t>P = 136.894 kW ;  Q = 70.006 kvar ;  S = 153.755 kVA</t>
-  </si>
-  <si>
-    <t>Corriente suministrada</t>
-  </si>
-  <si>
-    <t>I = S / (√3 · V)</t>
-  </si>
-  <si>
-    <t>I = 153 755 / (√3 · 23 000)</t>
-  </si>
-  <si>
-    <t>3.86 A</t>
-  </si>
-  <si>
-    <t>TR-1</t>
-  </si>
-  <si>
-    <t>Transformador</t>
-  </si>
-  <si>
-    <t>TR-1: impedancia del transformador</t>
-  </si>
-  <si>
-    <t>Separación de %Z</t>
-  </si>
-  <si>
-    <t>%R = %Z / √(1 + (X/R)²) ;  %X = %R · X/R</t>
-  </si>
-  <si>
-    <t>%R = 5.75 / √(1 + 6²)</t>
-  </si>
-  <si>
-    <t>%R = 0.9453 % ;  %X = 5.6718 %</t>
-  </si>
-  <si>
-    <t>Impedancia base del secundario</t>
-  </si>
-  <si>
-    <t>Zb = V² / Sn</t>
-  </si>
-  <si>
-    <t>Zb = 480.0² / 750 000</t>
-  </si>
-  <si>
-    <t>0.30720 Ω</t>
-  </si>
-  <si>
-    <t>Impedancia referida al secundario</t>
-  </si>
-  <si>
-    <t>R = 0.00290 Ω ;  X = 0.01742 Ω</t>
-  </si>
-  <si>
-    <t>TR-1: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>Potencia aguas abajo</t>
-  </si>
-  <si>
-    <t>P = 136.894 kW ;  Q = 70.006 kvar ;  S = 153.755 kVA ;  FP = 0.8903</t>
-  </si>
-  <si>
-    <t>Corriente</t>
-  </si>
-  <si>
-    <t>I = 153 755.2 / (√3 · 480.0)</t>
-  </si>
-  <si>
-    <t>184.94 A</t>
-  </si>
-  <si>
-    <t>Corriente del primario</t>
-  </si>
-  <si>
-    <t>Regulación del transformador</t>
-  </si>
-  <si>
-    <t>%ΔV ≈ (S / Sn) · (%R · cosφ + %X · senφ)</t>
-  </si>
-  <si>
-    <t>%ΔV = (153 755 / 750 000) · (0.9453 · 0.8903 + 5.6718 · 0.4553)</t>
-  </si>
-  <si>
-    <t>0.702 %</t>
-  </si>
-  <si>
-    <t>Tablero</t>
-  </si>
-  <si>
-    <t>TG: tensión en barras</t>
-  </si>
-  <si>
-    <t>Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>476.6 V (99.30 % de 480 V)</t>
-  </si>
-  <si>
-    <t>Interruptor / protección</t>
-  </si>
-  <si>
-    <t>Selección de la protección</t>
-  </si>
-  <si>
-    <t>Corriente de diseño del alimentador (430-24)</t>
-  </si>
-  <si>
-    <t>I_d = 1.25 · I_mayor + Σ I_otros motores + I_no continua + 1.25 · I_continua</t>
-  </si>
-  <si>
-    <t>I_d = 1.25 · 65.00 (M-01) + 45.36 + 0.00 + 1.25 · 0.00</t>
-  </si>
-  <si>
-    <t>126.61 A</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 430-24</t>
-  </si>
-  <si>
-    <t>Protección máxima del alimentador (430-62(a), 430-63)</t>
-  </si>
-  <si>
-    <t>I_prot ≤ mayor protección de derivado + Σ demás corrientes de motores + otras cargas</t>
-  </si>
-  <si>
-    <t>175 A (AL-11) + 45.36 + 0.00 = 220.36 A</t>
-  </si>
-  <si>
-    <t>200 A (valor estándar no mayor)</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 430-62(a) · 430-63 · 240-6(a)</t>
-  </si>
-  <si>
-    <t>INT-1: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>P = 80.598 kW ;  Q = 42.740 kvar ;  S = 91.229 kVA ;  FP = 0.8835</t>
-  </si>
-  <si>
-    <t>I = 91 228.8 / (√3 · 480.0)</t>
-  </si>
-  <si>
-    <t>109.73 A</t>
-  </si>
-  <si>
-    <t>Caída de tensión</t>
-  </si>
-  <si>
-    <t>Sin impedancia (0 %)</t>
-  </si>
-  <si>
-    <t>Corriente nominal del primario</t>
-  </si>
-  <si>
-    <t>I = Sn / (√3 · V)</t>
-  </si>
-  <si>
-    <t>I = 75 000 / (√3 · 480)</t>
-  </si>
-  <si>
-    <t>90.21 A</t>
-  </si>
-  <si>
-    <t>Protección máxima del primario</t>
-  </si>
-  <si>
-    <t>I_prot ≤ 125 % · I_pri (si no es estándar, el inmediato superior: Tabla 450-3(b) nota 1)</t>
-  </si>
-  <si>
-    <t>1.25 · 90.21 = 112.76 A</t>
-  </si>
-  <si>
-    <t>125 A</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 Tabla 450-3(b) · 240-6(a)</t>
-  </si>
-  <si>
-    <t>INT-2: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>P = 17.296 kW ;  Q = 8.377 kvar ;  S = 19.218 kVA ;  FP = 0.9000</t>
-  </si>
-  <si>
-    <t>I = 19 217.8 / (√3 · 480.0)</t>
-  </si>
-  <si>
-    <t>23.12 A</t>
-  </si>
-  <si>
-    <t>L-02: corriente</t>
-  </si>
-  <si>
-    <t>4.01 A — continua (alumbrado: continua por defecto)</t>
-  </si>
-  <si>
-    <t>CA-01: corriente</t>
-  </si>
-  <si>
-    <t>48.11 A — no continua (no continua por defecto)</t>
-  </si>
-  <si>
-    <t>Corriente de diseño</t>
-  </si>
-  <si>
-    <t>I_d = I_no continua + 1.25 · I_continua</t>
-  </si>
-  <si>
-    <t>I_d = 48.11 + 1.25 · 4.01</t>
-  </si>
-  <si>
-    <t>53.12 A</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 215-2(a)(1)</t>
-  </si>
-  <si>
-    <t>I_prot ≥ I_d (valor estándar inmediato)</t>
-  </si>
-  <si>
-    <t>60 A</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 215-3 · 240-6(a)</t>
-  </si>
-  <si>
-    <t>INT-4: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>P = 39.000 kW ;  Q = 18.889 kvar ;  S = 43.333 kVA ;  FP = 0.9000</t>
-  </si>
-  <si>
-    <t>I = 43 333.3 / (√3 · 480.0)</t>
-  </si>
-  <si>
-    <t>52.12 A</t>
-  </si>
-  <si>
-    <t>Alimentador (cable)</t>
-  </si>
-  <si>
-    <t>Dimensionamiento</t>
-  </si>
-  <si>
-    <t>Temperatura nominal del conductor</t>
-  </si>
-  <si>
-    <t>THHW-LS: 75 °C lugares mojados; 90 °C lugares secos</t>
-  </si>
-  <si>
-    <t>90 °C</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 Tabla 310-104(a) · Se toma la mayor temperatura del aislamiento; en lugares mojados aplica la indicada para ellos.</t>
-  </si>
-  <si>
-    <t>Temperatura de terminales</t>
-  </si>
-  <si>
-    <t>circuito de 200 A &gt; 100 A (110-14(c)(1)(b))</t>
-  </si>
-  <si>
-    <t>75 °C</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 110-14(c)</t>
-  </si>
-  <si>
-    <t>Factor de corrección por temperatura ambiente</t>
-  </si>
-  <si>
-    <t>30 °C (temperatura ambiente del proyecto), columna de 90 °C</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 Tabla 310-15(b)(2)(a)</t>
-  </si>
-  <si>
-    <t>Factor de ajuste por agrupamiento</t>
-  </si>
-  <si>
-    <t>3 conductores portadores de corriente en la canalización</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 Tabla 310-15(b)(3)(a)</t>
-  </si>
-  <si>
-    <t>Verificación del calibre fijado</t>
-  </si>
-  <si>
-    <t>2/0 AWG: 90 °C → 195 A · 1 · 1 = 195.00 A ; terminales 75 °C: 175.00 A ; ampacidad = 175.00 A</t>
-  </si>
-  <si>
-    <t>Cumple ampacidad y protección</t>
-  </si>
-  <si>
-    <t>Caída de tensión con el calibre elegido</t>
-  </si>
-  <si>
-    <t>0.593 % ≤ 3 % (NOM-001-SEDE-2012 215-2(a)(1) Nota 2 (recomendación))</t>
-  </si>
-  <si>
-    <t>Conductor de puesta a tierra de equipos</t>
-  </si>
-  <si>
-    <t>200 A → 6 AWG Cu (13.3 mm²) ; aumento proporcional (250-122(b)): 13.30 · 67.43 / 42.41 = 21.15 mm² → 4</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 Tabla 250-122</t>
-  </si>
-  <si>
-    <t>AL-1: impedancia del conductor</t>
-  </si>
-  <si>
-    <t>Resistencia y reactancia por conductor</t>
-  </si>
-  <si>
-    <t>2/0 Cu, conduit de acero, 75 °C</t>
-  </si>
-  <si>
-    <t>R = 0.33 Ω/km ;  XL = 0.177 Ω/km</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 Capítulo 10, Tabla 9</t>
-  </si>
-  <si>
-    <t>Impedancia del tramo</t>
-  </si>
-  <si>
-    <t>Z = (R + jXL) · L / n</t>
-  </si>
-  <si>
-    <t>Z = (0.33 + j0.177) · 0.0400 km / 1</t>
-  </si>
-  <si>
-    <t>R = 0.01320 Ω ;  X = 0.00708 Ω</t>
-  </si>
-  <si>
-    <t>AL-1: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>Caída de tensión (impedancia eficaz)</t>
-  </si>
-  <si>
-    <t>ΔV = I · (R·cosφ + X·senφ) ;  %ΔV = ΔV / V_fn · 100</t>
-  </si>
-  <si>
-    <t>ΔV = 109.73 · (0.01320 · 0.8835 + 0.00708 · 0.4685) = 1.644 V ;  %ΔV = 1.644 / 277.13 · 100</t>
-  </si>
-  <si>
-    <t>0.593 %</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 Capítulo 10, Tabla 9, nota 2</t>
-  </si>
-  <si>
-    <t>Centro de control de motores (CCM)</t>
-  </si>
-  <si>
-    <t>CCM-1: tensión en barras</t>
-  </si>
-  <si>
-    <t>473.8 V (98.70 % de 480 V)</t>
-  </si>
-  <si>
-    <t>circuito de 125 A &gt; 100 A (110-14(c)(1)(b))</t>
-  </si>
-  <si>
-    <t>2 AWG: 90 °C → 130 A · 1 · 1 = 130.00 A ; terminales 75 °C: 115.00 A ; ampacidad = 115.00 A</t>
-  </si>
-  <si>
-    <t>0.113 % ≤ 3 % (NOM-001-SEDE-2012 215-2(a)(1) Nota 2 (recomendación))</t>
-  </si>
-  <si>
-    <t>125 A → 6 AWG Cu (13.3 mm²)</t>
-  </si>
-  <si>
-    <t>AL-2: impedancia del conductor</t>
-  </si>
-  <si>
-    <t>2 Cu, conduit de acero, 75 °C</t>
-  </si>
-  <si>
-    <t>R = 0.66 Ω/km ;  XL = 0.187 Ω/km</t>
-  </si>
-  <si>
-    <t>Z = (0.66 + j0.187) · 0.0200 km / 1</t>
-  </si>
-  <si>
-    <t>R = 0.01320 Ω ;  X = 0.00374 Ω</t>
-  </si>
-  <si>
-    <t>AL-2: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>ΔV = 23.12 · (0.01320 · 0.9000 + 0.00374 · 0.4359) = 0.312 V ;  %ΔV = 0.312 / 277.13 · 100</t>
-  </si>
-  <si>
-    <t>0.113 %</t>
-  </si>
-  <si>
-    <t>circuito de 60 A ≤ 100 A (110-14(c)(1)(a))</t>
-  </si>
-  <si>
-    <t>60 °C</t>
-  </si>
-  <si>
-    <t>4 AWG: 90 °C → 95 A · 1 · 1 = 95.00 A ; terminales 60 °C: 70.00 A ; ampacidad = 70.00 A</t>
-  </si>
-  <si>
-    <t>0.928 % ≤ 3 % (NOM-001-SEDE-2012 215-2(a)(1) Nota 2 (recomendación))</t>
-  </si>
-  <si>
-    <t>60 A → 10 AWG Cu (5.26 mm²) ; aumento proporcional (250-122(b)): 5.26 · 21.15 / 13.30 = 8.36 mm² → 8</t>
-  </si>
-  <si>
-    <t>AL-4: impedancia del conductor</t>
-  </si>
-  <si>
-    <t>4 Cu, conduit de PVC, 75 °C</t>
-  </si>
-  <si>
-    <t>R = 1.02 Ω/km ;  XL = 0.157 Ω/km</t>
-  </si>
-  <si>
-    <t>Z = (1.02 + j0.157) · 0.0500 km / 1</t>
-  </si>
-  <si>
-    <t>R = 0.05100 Ω ;  X = 0.00785 Ω</t>
-  </si>
-  <si>
-    <t>AL-4: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>ΔV = 52.12 · (0.05100 · 0.9000 + 0.00785 · 0.4359) = 2.571 V ;  %ΔV = 2.571 / 277.13 · 100</t>
-  </si>
-  <si>
-    <t>0.928 %</t>
-  </si>
-  <si>
-    <t>TAB-B: tensión en barras</t>
-  </si>
-  <si>
-    <t>472.2 V (98.37 % de 480 V)</t>
-  </si>
-  <si>
-    <t>Corriente de diseño del conductor</t>
-  </si>
-  <si>
-    <t>I_d = 1.25 · I</t>
-  </si>
-  <si>
-    <t>I_d = 1.25 · 65.00 (corriente de tabla)</t>
-  </si>
-  <si>
-    <t>81.25 A</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 430-22</t>
-  </si>
-  <si>
-    <t>Protección contra cortocircuito y falla a tierra</t>
-  </si>
-  <si>
-    <t>I_prot ≤ 250 % · I_pc ; si no es estándar, el inmediato superior (430-52(c)(1) Exc. 1)</t>
-  </si>
-  <si>
-    <t>2.5 · 65.00 = 162.50 A (Interruptor automático de tiempo inverso², De jaula de ardilla: diferentes de los de diseño B energéticamente eficientes)</t>
-  </si>
-  <si>
-    <t>175 A</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 Tabla 430-52 · 240-6(a)</t>
-  </si>
-  <si>
-    <t>INT-11: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>P = 45.934 kW ;  Q = 28.467 kvar ;  S = 54.040 kVA ;  FP = 0.8500</t>
-  </si>
-  <si>
-    <t>I = 54 040.0 / (√3 · 480.0)</t>
-  </si>
-  <si>
-    <t>65.00 A</t>
-  </si>
-  <si>
-    <t>I_d = 1.25 · I_ent</t>
-  </si>
-  <si>
-    <t>I_d = 1.25 · 31.36 (corriente de entrada calculada con la carga (no se capturó la de placa))</t>
-  </si>
-  <si>
-    <t>39.20 A</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 430-122(a)</t>
-  </si>
-  <si>
-    <t>Protección propuesta</t>
-  </si>
-  <si>
-    <t>40 A</t>
-  </si>
-  <si>
-    <t>Valor estándar ≥ corriente de diseño (240-6(a)). Confirmar con las instrucciones del fabricante del variador (430-130).</t>
-  </si>
-  <si>
-    <t>INT-12: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>P = 24.770 kW ;  Q = 8.142 kvar ;  S = 26.074 kVA ;  FP = 0.9500</t>
-  </si>
-  <si>
-    <t>I = 26 073.8 / (√3 · 480.0)</t>
-  </si>
-  <si>
-    <t>31.36 A</t>
-  </si>
-  <si>
-    <t>I_d = 1.25 · 14.00 (corriente de tabla)</t>
-  </si>
-  <si>
-    <t>17.50 A</t>
-  </si>
-  <si>
-    <t>2.5 · 14.00 = 35.00 A (Interruptor automático de tiempo inverso², De jaula de ardilla: diferentes de los de diseño B energéticamente eficientes)</t>
-  </si>
-  <si>
-    <t>35 A</t>
-  </si>
-  <si>
-    <t>INT-13: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>P = 9.893 kW ;  Q = 6.131 kvar ;  S = 11.639 kVA ;  FP = 0.8500</t>
-  </si>
-  <si>
-    <t>I = 11 639.4 / (√3 · 480.0)</t>
-  </si>
-  <si>
-    <t>14.00 A</t>
-  </si>
-  <si>
-    <t>TR-2: impedancia del transformador</t>
-  </si>
-  <si>
-    <t>%R = 4 / √(1 + 2²)</t>
-  </si>
-  <si>
-    <t>%R = 1.7889 % ;  %X = 3.5777 %</t>
-  </si>
-  <si>
-    <t>Zb = 220.0² / 75 000</t>
-  </si>
-  <si>
-    <t>0.64533 Ω</t>
-  </si>
-  <si>
-    <t>R = 0.01154 Ω ;  X = 0.02309 Ω</t>
-  </si>
-  <si>
-    <t>TR-2: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>I = 19 217.8 / (√3 · 220.0)</t>
-  </si>
-  <si>
-    <t>50.43 A</t>
-  </si>
-  <si>
-    <t>%ΔV = (19 218 / 75 000) · (1.7889 · 0.9000 + 3.5777 · 0.4359)</t>
-  </si>
-  <si>
-    <t>0.812 %</t>
-  </si>
-  <si>
-    <t>12.03 A — continua (alumbrado: continua por defecto)</t>
-  </si>
-  <si>
-    <t>I_d = 0.00 + 1.25 · 12.03</t>
-  </si>
-  <si>
-    <t>15.04 A</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 210-19(a)(1)</t>
-  </si>
-  <si>
-    <t>16 A</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 210-20(a) · 240-6(a)</t>
-  </si>
-  <si>
-    <t>INT-41: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>P = 3.000 kW ;  Q = 1.453 kvar ;  S = 3.333 kVA ;  FP = 0.9000</t>
-  </si>
-  <si>
-    <t>I = S / V</t>
-  </si>
-  <si>
-    <t>I = 3 333.3 / 277.1</t>
-  </si>
-  <si>
-    <t>12.03 A</t>
-  </si>
-  <si>
-    <t>I_d = 48.11 + 1.25 · 0.00</t>
-  </si>
-  <si>
-    <t>48.11 A</t>
-  </si>
-  <si>
-    <t>50 A</t>
-  </si>
-  <si>
-    <t>INT-42: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>P = 36.000 kW ;  Q = 17.436 kvar ;  S = 40.000 kVA ;  FP = 0.9000</t>
-  </si>
-  <si>
-    <t>I = 40 000.0 / (√3 · 480.0)</t>
-  </si>
-  <si>
-    <t>motor con letra de diseño B: se permiten 75 °C (110-14(c)(1)(a)(4))</t>
-  </si>
-  <si>
-    <t>4 AWG: 90 °C → 95 A · 1 · 1 = 95.00 A ; terminales 75 °C: 85.00 A ; ampacidad = 85.00 A</t>
-  </si>
-  <si>
-    <t>0.569 % ≤ 3 % (NOM-001-SEDE-2012 210-19(a) Nota 4 (recomendación))</t>
-  </si>
-  <si>
-    <t>175 A → 6 AWG Cu (13.3 mm²)</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 Tabla 250-122 · 250-122(d)(1)</t>
-  </si>
-  <si>
-    <t>AL-11: impedancia del conductor</t>
-  </si>
-  <si>
-    <t>4 Cu, conduit de acero, 75 °C</t>
-  </si>
-  <si>
-    <t>R = 1.02 Ω/km ;  XL = 0.197 Ω/km</t>
-  </si>
-  <si>
-    <t>Z = (1.02 + j0.197) · 0.0250 km / 1</t>
-  </si>
-  <si>
-    <t>R = 0.02550 Ω ;  X = 0.00493 Ω</t>
-  </si>
-  <si>
-    <t>AL-11: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>ΔV = 65.00 · (0.02550 · 0.8500 + 0.00493 · 0.5268) = 1.578 V ;  %ΔV = 1.578 / 277.13 · 100</t>
-  </si>
-  <si>
-    <t>0.569 %</t>
-  </si>
-  <si>
-    <t>Motor</t>
-  </si>
-  <si>
-    <t>M-01: potencia demandada</t>
-  </si>
-  <si>
-    <t>Corriente a plena carga del motor (tabla)</t>
-  </si>
-  <si>
-    <t>50 hp, trifásico, columna de 460 V</t>
-  </si>
-  <si>
-    <t>65.0 A</t>
-  </si>
-  <si>
-    <t>NOM-001-SEDE-2012 Tabla 430-250 · 430-6(a)(1)</t>
-  </si>
-  <si>
-    <t>Potencia aparente a la tensión nominal del sistema</t>
-  </si>
-  <si>
-    <t>S = √3 · V_sis · I</t>
-  </si>
-  <si>
-    <t>S = √3 · 480 · 65.0</t>
-  </si>
-  <si>
-    <t>54.040 kVA</t>
-  </si>
-  <si>
-    <t>Potencias activa y reactiva</t>
-  </si>
-  <si>
-    <t>P = S · FP ;  Q = S · sen(arccos FP)</t>
-  </si>
-  <si>
-    <t>P = 54 040.0 · 0.85 ;  Q = 54 040.0 · 0.5268</t>
-  </si>
-  <si>
-    <t>P = 45.934 kW ;  Q = 28.467 kvar</t>
-  </si>
-  <si>
-    <t>M-01: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>Corriente de la carga</t>
-  </si>
-  <si>
-    <t>Tensión en terminales</t>
-  </si>
-  <si>
-    <t>471.1 V (98.14 % de 480.0 V entre fases)</t>
-  </si>
-  <si>
-    <t>Caída acumulada en conductores desde el origen de la zona</t>
-  </si>
-  <si>
-    <t>1.162 %</t>
-  </si>
-  <si>
-    <t>circuito de 40 A ≤ 100 A (110-14(c)(1)(a))</t>
-  </si>
-  <si>
-    <t>8 AWG: 90 °C → 55 A · 1 · 1 = 55.00 A ; terminales 60 °C: 40.00 A ; ampacidad = 40.00 A</t>
-  </si>
-  <si>
-    <t>0.848 % ≤ 3 % (NOM-001-SEDE-2012 210-19(a) Nota 4 (recomendación))</t>
-  </si>
-  <si>
-    <t>40 A → 10 AWG Cu (5.26 mm²)</t>
-  </si>
-  <si>
-    <t>AL-12: impedancia del conductor</t>
-  </si>
-  <si>
-    <t>8 Cu, conduit de acero, 75 °C</t>
-  </si>
-  <si>
-    <t>R = 2.56 Ω/km ;  XL = 0.213 Ω/km</t>
-  </si>
-  <si>
-    <t>Z = (2.56 + j0.213) · 0.0300 km / 1</t>
-  </si>
-  <si>
-    <t>R = 0.07680 Ω ;  X = 0.00639 Ω</t>
-  </si>
-  <si>
-    <t>AL-12: Método nominal (cálculo a mano)</t>
-  </si>
-  <si>
-    <t>ΔV = 31.36 · (0.07680 · 0.9500 + 0.00639 · 0.3122) = 2.351 V ;  %ΔV = 2.351 / 277.13 · 100</t>
-  </si>
-  <si>
-    <t>0.848 %</t>
-  </si>
-  <si>
-    <t>12 AWG: 90 °C → 30 A · 1 · 1 = 30.00 A ; terminales 75 °C: 25.00 A ; ampacidad = 25.00 A</t>
-  </si>
-  <si>
-    <t>0.868 % ≤ 3 % (NOM-001-SEDE-2012 210-19(a) Nota 4 (recomendación))</t>
-  </si>
-  <si>
-    <t>35 A → 10 AWG Cu (5.26 mm²) ; aumento proporcional (250-122(b)): 5.26 · 3.31 / 2.08 = 8.37 mm² → 6 ; no se exige mayor que la fase (250-122(a)) → 12</t>
   </si>
   <si>
     <t>AL-13: impedancia del conductor</t>
@@ -5587,10 +5602,10 @@
         <v>299</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>89</v>
+        <v>300</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -5601,25 +5616,25 @@
         <v>276</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D40" s="8">
         <v>1</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -5630,22 +5645,22 @@
         <v>276</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D41" s="8">
         <v>2</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>192</v>
@@ -5659,7 +5674,7 @@
         <v>276</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D42" s="8">
         <v>1</v>
@@ -5688,7 +5703,7 @@
         <v>276</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D43" s="8">
         <v>2</v>
@@ -5717,25 +5732,25 @@
         <v>276</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D44" s="8">
         <v>3</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -5743,10 +5758,10 @@
         <v>85</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D45" s="8">
         <v>1</v>
@@ -5761,7 +5776,7 @@
         <v>192</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>192</v>
@@ -5874,7 +5889,7 @@
         <v>192</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H49" s="8" t="s">
         <v>284</v>
@@ -5961,7 +5976,7 @@
         <v>192</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>295</v>
@@ -5993,7 +6008,7 @@
         <v>192</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>192</v>
@@ -6019,13 +6034,13 @@
         <v>192</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>96</v>
+        <v>324</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -6036,25 +6051,25 @@
         <v>276</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D55" s="8">
         <v>1</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -6065,22 +6080,22 @@
         <v>276</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D56" s="8">
         <v>2</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>192</v>
@@ -6094,7 +6109,7 @@
         <v>276</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D57" s="8">
         <v>1</v>
@@ -6123,7 +6138,7 @@
         <v>276</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D58" s="8">
         <v>2</v>
@@ -6152,25 +6167,25 @@
         <v>276</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D59" s="8">
         <v>3</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -6338,10 +6353,10 @@
         <v>192</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>285</v>
@@ -6425,7 +6440,7 @@
         <v>192</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H68" s="8" t="s">
         <v>295</v>
@@ -6457,7 +6472,7 @@
         <v>192</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>192</v>
@@ -6483,13 +6498,13 @@
         <v>192</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>102</v>
+        <v>338</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -6500,25 +6515,25 @@
         <v>276</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D71" s="8">
         <v>1</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -6529,22 +6544,22 @@
         <v>276</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D72" s="8">
         <v>2</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>192</v>
@@ -6558,7 +6573,7 @@
         <v>276</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D73" s="8">
         <v>1</v>
@@ -6587,7 +6602,7 @@
         <v>276</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D74" s="8">
         <v>2</v>
@@ -6616,25 +6631,25 @@
         <v>276</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D75" s="8">
         <v>3</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -6645,7 +6660,7 @@
         <v>225</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D76" s="8">
         <v>1</v>
@@ -6660,7 +6675,7 @@
         <v>192</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I76" s="8" t="s">
         <v>192</v>
@@ -6680,19 +6695,19 @@
         <v>1</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -6709,19 +6724,19 @@
         <v>2</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -6732,7 +6747,7 @@
         <v>229</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D79" s="8">
         <v>1</v>
@@ -6747,7 +6762,7 @@
         <v>192</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I79" s="8" t="s">
         <v>192</v>
@@ -6761,7 +6776,7 @@
         <v>229</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D80" s="8">
         <v>2</v>
@@ -6773,10 +6788,10 @@
         <v>198</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I80" s="8" t="s">
         <v>192</v>
@@ -6790,7 +6805,7 @@
         <v>229</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D81" s="8">
         <v>3</v>
@@ -6825,19 +6840,19 @@
         <v>1</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -6854,7 +6869,7 @@
         <v>2</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>192</v>
@@ -6863,10 +6878,10 @@
         <v>192</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -6877,7 +6892,7 @@
         <v>229</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D84" s="8">
         <v>1</v>
@@ -6892,7 +6907,7 @@
         <v>192</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I84" s="8" t="s">
         <v>192</v>
@@ -6906,7 +6921,7 @@
         <v>229</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D85" s="8">
         <v>2</v>
@@ -6918,10 +6933,10 @@
         <v>198</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>192</v>
@@ -6935,7 +6950,7 @@
         <v>229</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D86" s="8">
         <v>3</v>
@@ -6970,19 +6985,19 @@
         <v>1</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -6999,19 +7014,19 @@
         <v>2</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -7022,7 +7037,7 @@
         <v>229</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D89" s="8">
         <v>1</v>
@@ -7037,7 +7052,7 @@
         <v>192</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I89" s="8" t="s">
         <v>192</v>
@@ -7051,7 +7066,7 @@
         <v>229</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D90" s="8">
         <v>2</v>
@@ -7063,10 +7078,10 @@
         <v>198</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I90" s="8" t="s">
         <v>192</v>
@@ -7080,7 +7095,7 @@
         <v>229</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D91" s="8">
         <v>3</v>
@@ -7109,7 +7124,7 @@
         <v>202</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D92" s="8">
         <v>1</v>
@@ -7121,10 +7136,10 @@
         <v>205</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="I92" s="8" t="s">
         <v>192</v>
@@ -7138,7 +7153,7 @@
         <v>202</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D93" s="8">
         <v>2</v>
@@ -7150,10 +7165,10 @@
         <v>209</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="I93" s="8" t="s">
         <v>192</v>
@@ -7167,7 +7182,7 @@
         <v>202</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D94" s="8">
         <v>3</v>
@@ -7182,7 +7197,7 @@
         <v>192</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="I94" s="8" t="s">
         <v>192</v>
@@ -7196,7 +7211,7 @@
         <v>202</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D95" s="8">
         <v>1</v>
@@ -7225,7 +7240,7 @@
         <v>202</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D96" s="8">
         <v>2</v>
@@ -7237,10 +7252,10 @@
         <v>198</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I96" s="8" t="s">
         <v>192</v>
@@ -7254,7 +7269,7 @@
         <v>202</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D97" s="8">
         <v>3</v>
@@ -7283,7 +7298,7 @@
         <v>202</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D98" s="8">
         <v>4</v>
@@ -7295,10 +7310,10 @@
         <v>222</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I98" s="8" t="s">
         <v>192</v>
@@ -7327,7 +7342,7 @@
         <v>192</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="I99" s="8" t="s">
         <v>192</v>
@@ -7353,13 +7368,13 @@
         <v>265</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -7385,10 +7400,10 @@
         <v>192</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -7399,7 +7414,7 @@
         <v>229</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D102" s="8">
         <v>1</v>
@@ -7414,7 +7429,7 @@
         <v>192</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I102" s="8" t="s">
         <v>192</v>
@@ -7428,7 +7443,7 @@
         <v>229</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D103" s="8">
         <v>2</v>
@@ -7437,13 +7452,13 @@
         <v>217</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I103" s="8" t="s">
         <v>192</v>
@@ -7457,7 +7472,7 @@
         <v>229</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D104" s="8">
         <v>3</v>
@@ -7527,13 +7542,13 @@
         <v>265</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -7559,10 +7574,10 @@
         <v>192</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
@@ -7573,7 +7588,7 @@
         <v>229</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D108" s="8">
         <v>1</v>
@@ -7588,7 +7603,7 @@
         <v>192</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I108" s="8" t="s">
         <v>192</v>
@@ -7602,7 +7617,7 @@
         <v>229</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D109" s="8">
         <v>2</v>
@@ -7614,10 +7629,10 @@
         <v>198</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="H109" s="8" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I109" s="8" t="s">
         <v>192</v>
@@ -7631,7 +7646,7 @@
         <v>229</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D110" s="8">
         <v>3</v>
@@ -7666,19 +7681,19 @@
         <v>1</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -7695,19 +7710,19 @@
         <v>2</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -7759,7 +7774,7 @@
         <v>192</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H114" s="8" t="s">
         <v>284</v>
@@ -7846,7 +7861,7 @@
         <v>192</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="H117" s="8" t="s">
         <v>295</v>
@@ -7878,7 +7893,7 @@
         <v>192</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="I118" s="8" t="s">
         <v>192</v>
@@ -7904,13 +7919,13 @@
         <v>192</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>96</v>
+        <v>324</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -7921,25 +7936,25 @@
         <v>276</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D120" s="8">
         <v>1</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -7950,22 +7965,22 @@
         <v>276</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D121" s="8">
         <v>2</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="I121" s="8" t="s">
         <v>192</v>
@@ -7979,7 +7994,7 @@
         <v>276</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D122" s="8">
         <v>1</v>
@@ -7994,7 +8009,7 @@
         <v>192</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I122" s="8" t="s">
         <v>192</v>
@@ -8008,7 +8023,7 @@
         <v>276</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D123" s="8">
         <v>2</v>
@@ -8020,10 +8035,10 @@
         <v>198</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I123" s="8" t="s">
         <v>192</v>
@@ -8037,25 +8052,25 @@
         <v>276</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D124" s="8">
         <v>3</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -8063,28 +8078,28 @@
         <v>105</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D125" s="8">
         <v>1</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -8092,25 +8107,25 @@
         <v>105</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D126" s="8">
         <v>2</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="I126" s="8" t="s">
         <v>192</v>
@@ -8121,25 +8136,25 @@
         <v>105</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D127" s="8">
         <v>3</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G127" s="6" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="H127" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="I127" s="8" t="s">
         <v>192</v>
@@ -8150,25 +8165,25 @@
         <v>105</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D128" s="8">
         <v>1</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I128" s="8" t="s">
         <v>192</v>
@@ -8179,16 +8194,16 @@
         <v>105</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D129" s="8">
         <v>2</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>192</v>
@@ -8197,7 +8212,7 @@
         <v>192</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="I129" s="8" t="s">
         <v>192</v>
@@ -8208,16 +8223,16 @@
         <v>105</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D130" s="8">
         <v>3</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F130" s="8" t="s">
         <v>192</v>
@@ -8226,7 +8241,7 @@
         <v>192</v>
       </c>
       <c r="H130" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="I130" s="8" t="s">
         <v>192</v>
@@ -8246,19 +8261,19 @@
         <v>1</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -8275,7 +8290,7 @@
         <v>2</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>192</v>
@@ -8284,10 +8299,10 @@
         <v>192</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
@@ -8339,10 +8354,10 @@
         <v>192</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="H134" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I134" s="8" t="s">
         <v>285</v>
@@ -8426,7 +8441,7 @@
         <v>192</v>
       </c>
       <c r="G137" s="6" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="H137" s="8" t="s">
         <v>295</v>
@@ -8458,7 +8473,7 @@
         <v>192</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="I138" s="8" t="s">
         <v>192</v>
@@ -8484,13 +8499,13 @@
         <v>192</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="H139" s="8" t="s">
-        <v>113</v>
+        <v>447</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
@@ -8501,25 +8516,25 @@
         <v>276</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D140" s="8">
         <v>1</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -8530,22 +8545,22 @@
         <v>276</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D141" s="8">
         <v>2</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="I141" s="8" t="s">
         <v>192</v>
@@ -8559,7 +8574,7 @@
         <v>276</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D142" s="8">
         <v>1</v>
@@ -8574,7 +8589,7 @@
         <v>192</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I142" s="8" t="s">
         <v>192</v>
@@ -8588,7 +8603,7 @@
         <v>276</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D143" s="8">
         <v>2</v>
@@ -8600,10 +8615,10 @@
         <v>198</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H143" s="8" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I143" s="8" t="s">
         <v>192</v>
@@ -8617,25 +8632,25 @@
         <v>276</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D144" s="8">
         <v>3</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H144" s="8" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -8652,19 +8667,19 @@
         <v>1</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="H145" s="8" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
@@ -8681,19 +8696,19 @@
         <v>2</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="H146" s="8" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
@@ -8745,7 +8760,7 @@
         <v>192</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H148" s="8" t="s">
         <v>284</v>
@@ -8832,7 +8847,7 @@
         <v>192</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="H151" s="8" t="s">
         <v>295</v>
@@ -8864,7 +8879,7 @@
         <v>192</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="I152" s="8" t="s">
         <v>192</v>
@@ -8890,13 +8905,13 @@
         <v>192</v>
       </c>
       <c r="G153" s="6" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="H153" s="8" t="s">
-        <v>118</v>
+        <v>459</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -8907,25 +8922,25 @@
         <v>276</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D154" s="8">
         <v>1</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F154" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -8936,22 +8951,22 @@
         <v>276</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D155" s="8">
         <v>2</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="I155" s="8" t="s">
         <v>192</v>
@@ -8965,7 +8980,7 @@
         <v>276</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D156" s="8">
         <v>1</v>
@@ -8980,7 +8995,7 @@
         <v>192</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I156" s="8" t="s">
         <v>192</v>
@@ -8994,7 +9009,7 @@
         <v>276</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D157" s="8">
         <v>2</v>
@@ -9006,10 +9021,10 @@
         <v>198</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="H157" s="8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I157" s="8" t="s">
         <v>192</v>
@@ -9023,25 +9038,25 @@
         <v>276</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D158" s="8">
         <v>3</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="H158" s="8" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
@@ -9049,28 +9064,28 @@
         <v>116</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D159" s="8">
         <v>1</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F159" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -9078,25 +9093,25 @@
         <v>116</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D160" s="8">
         <v>2</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="I160" s="8" t="s">
         <v>192</v>
@@ -9107,25 +9122,25 @@
         <v>116</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D161" s="8">
         <v>3</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G161" s="6" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="I161" s="8" t="s">
         <v>192</v>
@@ -9136,25 +9151,25 @@
         <v>116</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D162" s="8">
         <v>1</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I162" s="8" t="s">
         <v>192</v>
@@ -9165,16 +9180,16 @@
         <v>116</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D163" s="8">
         <v>2</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>192</v>
@@ -9183,7 +9198,7 @@
         <v>192</v>
       </c>
       <c r="H163" s="6" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="I163" s="8" t="s">
         <v>192</v>
@@ -9194,16 +9209,16 @@
         <v>116</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D164" s="8">
         <v>3</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F164" s="8" t="s">
         <v>192</v>
@@ -9212,7 +9227,7 @@
         <v>192</v>
       </c>
       <c r="H164" s="8" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="I164" s="8" t="s">
         <v>192</v>
@@ -9232,7 +9247,7 @@
         <v>1</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>192</v>
@@ -9241,7 +9256,7 @@
         <v>192</v>
       </c>
       <c r="H165" s="6" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I165" s="8" t="s">
         <v>192</v>
@@ -9261,7 +9276,7 @@
         <v>2</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>192</v>
@@ -9270,7 +9285,7 @@
         <v>192</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="I166" s="8" t="s">
         <v>192</v>
@@ -9290,7 +9305,7 @@
         <v>3</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>192</v>
@@ -9299,7 +9314,7 @@
         <v>192</v>
       </c>
       <c r="H167" s="6" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="I167" s="8" t="s">
         <v>192</v>
@@ -9325,10 +9340,10 @@
         <v>265</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="H168" s="8" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="I168" s="8" t="s">
         <v>268</v>
@@ -9412,10 +9427,10 @@
         <v>192</v>
       </c>
       <c r="G171" s="6" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="H171" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I171" s="8" t="s">
         <v>285</v>
@@ -9499,7 +9514,7 @@
         <v>192</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="H174" s="8" t="s">
         <v>295</v>
@@ -9531,7 +9546,7 @@
         <v>192</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="I175" s="8" t="s">
         <v>192</v>
@@ -9545,25 +9560,25 @@
         <v>276</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D176" s="8">
         <v>1</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
@@ -9574,22 +9589,22 @@
         <v>276</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D177" s="8">
         <v>2</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F177" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G177" s="6" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="H177" s="8" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="I177" s="8" t="s">
         <v>192</v>
@@ -9603,7 +9618,7 @@
         <v>276</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D178" s="8">
         <v>1</v>
@@ -9632,7 +9647,7 @@
         <v>276</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D179" s="8">
         <v>2</v>
@@ -9644,10 +9659,10 @@
         <v>198</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="H179" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I179" s="8" t="s">
         <v>192</v>
@@ -9661,25 +9676,25 @@
         <v>276</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D180" s="8">
         <v>3</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="H180" s="8" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
@@ -9690,7 +9705,7 @@
         <v>225</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D181" s="8">
         <v>1</v>
@@ -9705,7 +9720,7 @@
         <v>192</v>
       </c>
       <c r="H181" s="8" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="I181" s="8" t="s">
         <v>192</v>
@@ -9734,7 +9749,7 @@
         <v>192</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="I182" s="8" t="s">
         <v>192</v>
@@ -9760,13 +9775,13 @@
         <v>265</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="I183" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
@@ -9792,10 +9807,10 @@
         <v>192</v>
       </c>
       <c r="H184" s="8" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -9847,10 +9862,10 @@
         <v>192</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I186" s="8" t="s">
         <v>285</v>
@@ -9905,7 +9920,7 @@
         <v>192</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="H188" s="8" t="s">
         <v>288</v>
@@ -9934,7 +9949,7 @@
         <v>192</v>
       </c>
       <c r="G189" s="6" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H189" s="8" t="s">
         <v>295</v>
@@ -9966,7 +9981,7 @@
         <v>192</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="I190" s="8" t="s">
         <v>192</v>
@@ -9992,13 +10007,13 @@
         <v>192</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="H191" s="8" t="s">
-        <v>118</v>
+        <v>459</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
@@ -10009,25 +10024,25 @@
         <v>276</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D192" s="8">
         <v>1</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
@@ -10038,22 +10053,22 @@
         <v>276</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D193" s="8">
         <v>2</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F193" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="H193" s="8" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="I193" s="8" t="s">
         <v>192</v>
@@ -10067,7 +10082,7 @@
         <v>276</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D194" s="8">
         <v>1</v>
@@ -10082,7 +10097,7 @@
         <v>192</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I194" s="8" t="s">
         <v>192</v>
@@ -10096,7 +10111,7 @@
         <v>276</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D195" s="8">
         <v>2</v>
@@ -10105,13 +10120,13 @@
         <v>217</v>
       </c>
       <c r="F195" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H195" s="8" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I195" s="8" t="s">
         <v>192</v>
@@ -10125,25 +10140,25 @@
         <v>276</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D196" s="8">
         <v>3</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="H196" s="8" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="I196" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -10151,25 +10166,25 @@
         <v>125</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D197" s="8">
         <v>1</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="F197" s="8" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="H197" s="8" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="I197" s="8" t="s">
         <v>192</v>
@@ -10180,25 +10195,25 @@
         <v>125</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D198" s="8">
         <v>2</v>
       </c>
       <c r="E198" s="8" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="I198" s="8" t="s">
         <v>192</v>
@@ -10209,25 +10224,25 @@
         <v>125</v>
       </c>
       <c r="B199" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D199" s="8">
         <v>3</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G199" s="6" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="H199" s="8" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="I199" s="8" t="s">
         <v>192</v>
@@ -10238,25 +10253,25 @@
         <v>125</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D200" s="8">
         <v>1</v>
       </c>
       <c r="E200" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F200" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H200" s="8" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I200" s="8" t="s">
         <v>192</v>
@@ -10267,16 +10282,16 @@
         <v>125</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D201" s="8">
         <v>2</v>
       </c>
       <c r="E201" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F201" s="8" t="s">
         <v>192</v>
@@ -10285,7 +10300,7 @@
         <v>192</v>
       </c>
       <c r="H201" s="6" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="I201" s="8" t="s">
         <v>192</v>
@@ -10296,16 +10311,16 @@
         <v>125</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D202" s="8">
         <v>3</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>192</v>
@@ -10314,7 +10329,7 @@
         <v>192</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="I202" s="8" t="s">
         <v>192</v>
@@ -10369,13 +10384,13 @@
         <v>265</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H204" s="8" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I204" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
@@ -10401,10 +10416,10 @@
         <v>192</v>
       </c>
       <c r="H205" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="I205" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
@@ -10456,10 +10471,10 @@
         <v>192</v>
       </c>
       <c r="G207" s="6" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="H207" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I207" s="8" t="s">
         <v>285</v>
@@ -10543,7 +10558,7 @@
         <v>192</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="H210" s="8" t="s">
         <v>295</v>
@@ -10575,7 +10590,7 @@
         <v>192</v>
       </c>
       <c r="H211" s="6" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="I211" s="8" t="s">
         <v>192</v>
@@ -10601,13 +10616,13 @@
         <v>192</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H212" s="8" t="s">
-        <v>113</v>
+        <v>447</v>
       </c>
       <c r="I212" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -10618,25 +10633,25 @@
         <v>276</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="D213" s="8">
         <v>1</v>
       </c>
       <c r="E213" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F213" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="H213" s="6" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="I213" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -10647,22 +10662,22 @@
         <v>276</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="D214" s="8">
         <v>2</v>
       </c>
       <c r="E214" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F214" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H214" s="8" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="I214" s="8" t="s">
         <v>192</v>
@@ -10676,7 +10691,7 @@
         <v>276</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D215" s="8">
         <v>1</v>
@@ -10691,7 +10706,7 @@
         <v>192</v>
       </c>
       <c r="H215" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I215" s="8" t="s">
         <v>192</v>
@@ -10705,7 +10720,7 @@
         <v>276</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D216" s="8">
         <v>2</v>
@@ -10717,10 +10732,10 @@
         <v>198</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="H216" s="8" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I216" s="8" t="s">
         <v>192</v>
@@ -10734,25 +10749,25 @@
         <v>276</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D217" s="8">
         <v>3</v>
       </c>
       <c r="E217" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G217" s="6" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="I217" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -10760,16 +10775,16 @@
         <v>129</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C218" s="8" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D218" s="8">
         <v>1</v>
       </c>
       <c r="E218" s="8" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>192</v>
@@ -10778,7 +10793,7 @@
         <v>192</v>
       </c>
       <c r="H218" s="8" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="I218" s="8" t="s">
         <v>192</v>
@@ -10789,25 +10804,25 @@
         <v>129</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C219" s="8" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D219" s="8">
         <v>2</v>
       </c>
       <c r="E219" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F219" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G219" s="6" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="H219" s="6" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="I219" s="8" t="s">
         <v>192</v>
@@ -10818,25 +10833,25 @@
         <v>129</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D220" s="8">
         <v>1</v>
       </c>
       <c r="E220" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F220" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="H220" s="8" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="I220" s="8" t="s">
         <v>192</v>
@@ -10847,16 +10862,16 @@
         <v>129</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D221" s="8">
         <v>2</v>
       </c>
       <c r="E221" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>192</v>
@@ -10865,7 +10880,7 @@
         <v>192</v>
       </c>
       <c r="H221" s="6" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="I221" s="8" t="s">
         <v>192</v>
@@ -10876,16 +10891,16 @@
         <v>129</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D222" s="8">
         <v>3</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>192</v>
@@ -10894,7 +10909,7 @@
         <v>192</v>
       </c>
       <c r="H222" s="8" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="I222" s="8" t="s">
         <v>192</v>
@@ -10905,10 +10920,10 @@
         <v>110</v>
       </c>
       <c r="B223" s="8" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D223" s="8">
         <v>1</v>
@@ -10923,7 +10938,7 @@
         <v>192</v>
       </c>
       <c r="H223" s="6" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="I223" s="8" t="s">
         <v>192</v>
@@ -10934,83 +10949,83 @@
         <v>110</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D224" s="8">
         <v>2</v>
       </c>
       <c r="E224" s="8" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="F224" s="6" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="G224" s="8" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="I224" s="6" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D225" s="8">
         <v>1</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G225" s="6" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="I225" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D226" s="8">
         <v>2</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F226" s="8" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G226" s="8" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="H226" s="8" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="I226" s="8" t="s">
         <v>192</v>
@@ -11018,28 +11033,28 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D227" s="8">
         <v>3</v>
       </c>
       <c r="E227" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F227" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G227" s="6" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="H227" s="6" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="I227" s="8" t="s">
         <v>192</v>
@@ -11047,28 +11062,28 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D228" s="8">
         <v>1</v>
       </c>
       <c r="E228" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F228" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G228" s="8" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="H228" s="8" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="I228" s="8" t="s">
         <v>192</v>
@@ -11076,19 +11091,19 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D229" s="8">
         <v>2</v>
       </c>
       <c r="E229" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>192</v>
@@ -11097,7 +11112,7 @@
         <v>192</v>
       </c>
       <c r="H229" s="6" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="I229" s="8" t="s">
         <v>192</v>
@@ -11105,19 +11120,19 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D230" s="8">
         <v>3</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F230" s="8" t="s">
         <v>192</v>
@@ -11126,7 +11141,7 @@
         <v>192</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="I230" s="8" t="s">
         <v>192</v>
@@ -11146,7 +11161,7 @@
         <v>1</v>
       </c>
       <c r="E231" s="8" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>192</v>
@@ -11155,7 +11170,7 @@
         <v>192</v>
       </c>
       <c r="H231" s="6" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="I231" s="8" t="s">
         <v>192</v>
@@ -11181,13 +11196,13 @@
         <v>265</v>
       </c>
       <c r="G232" s="8" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="H232" s="8" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="I232" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
@@ -11213,10 +11228,10 @@
         <v>192</v>
       </c>
       <c r="H233" s="8" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="I233" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
@@ -11227,7 +11242,7 @@
         <v>229</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D234" s="8">
         <v>1</v>
@@ -11242,7 +11257,7 @@
         <v>192</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="I234" s="8" t="s">
         <v>192</v>
@@ -11256,7 +11271,7 @@
         <v>229</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D235" s="8">
         <v>2</v>
@@ -11265,13 +11280,13 @@
         <v>217</v>
       </c>
       <c r="F235" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G235" s="8" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="H235" s="8" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="I235" s="8" t="s">
         <v>192</v>
@@ -11285,7 +11300,7 @@
         <v>229</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D236" s="8">
         <v>3</v>
@@ -11320,7 +11335,7 @@
         <v>1</v>
       </c>
       <c r="E237" s="8" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>192</v>
@@ -11329,7 +11344,7 @@
         <v>192</v>
       </c>
       <c r="H237" s="6" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I237" s="8" t="s">
         <v>192</v>
@@ -11355,13 +11370,13 @@
         <v>265</v>
       </c>
       <c r="G238" s="8" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="H238" s="8" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="I238" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
@@ -11387,10 +11402,10 @@
         <v>192</v>
       </c>
       <c r="H239" s="8" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="I239" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
@@ -11407,7 +11422,7 @@
         <v>4</v>
       </c>
       <c r="E240" s="8" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>192</v>
@@ -11416,7 +11431,7 @@
         <v>192</v>
       </c>
       <c r="H240" s="6" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="I240" s="8" t="s">
         <v>192</v>
@@ -11430,7 +11445,7 @@
         <v>229</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D241" s="8">
         <v>1</v>
@@ -11445,7 +11460,7 @@
         <v>192</v>
       </c>
       <c r="H241" s="6" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="I241" s="8" t="s">
         <v>192</v>
@@ -11459,7 +11474,7 @@
         <v>229</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D242" s="8">
         <v>2</v>
@@ -11468,13 +11483,13 @@
         <v>217</v>
       </c>
       <c r="F242" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G242" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="H242" s="8" t="s">
         <v>578</v>
-      </c>
-      <c r="H242" s="8" t="s">
-        <v>573</v>
       </c>
       <c r="I242" s="8" t="s">
         <v>192</v>
@@ -11488,7 +11503,7 @@
         <v>229</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D243" s="8">
         <v>3</v>
@@ -11523,7 +11538,7 @@
         <v>1</v>
       </c>
       <c r="E244" s="8" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>192</v>
@@ -11532,7 +11547,7 @@
         <v>192</v>
       </c>
       <c r="H244" s="6" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="I244" s="8" t="s">
         <v>192</v>
@@ -11558,13 +11573,13 @@
         <v>265</v>
       </c>
       <c r="G245" s="8" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="I245" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
@@ -11590,10 +11605,10 @@
         <v>192</v>
       </c>
       <c r="H246" s="8" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="I246" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
@@ -11604,7 +11619,7 @@
         <v>229</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D247" s="8">
         <v>1</v>
@@ -11619,7 +11634,7 @@
         <v>192</v>
       </c>
       <c r="H247" s="6" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="I247" s="8" t="s">
         <v>192</v>
@@ -11633,7 +11648,7 @@
         <v>229</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D248" s="8">
         <v>2</v>
@@ -11645,10 +11660,10 @@
         <v>198</v>
       </c>
       <c r="G248" s="8" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="H248" s="8" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="I248" s="8" t="s">
         <v>192</v>
@@ -11662,7 +11677,7 @@
         <v>229</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D249" s="8">
         <v>3</v>
@@ -11697,7 +11712,7 @@
         <v>1</v>
       </c>
       <c r="E250" s="8" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F250" s="8" t="s">
         <v>192</v>
@@ -11706,7 +11721,7 @@
         <v>192</v>
       </c>
       <c r="H250" s="6" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="I250" s="8" t="s">
         <v>192</v>
@@ -11732,13 +11747,13 @@
         <v>265</v>
       </c>
       <c r="G251" s="8" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="H251" s="8" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="I251" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
@@ -11764,10 +11779,10 @@
         <v>192</v>
       </c>
       <c r="H252" s="8" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="I252" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
@@ -11819,10 +11834,10 @@
         <v>192</v>
       </c>
       <c r="G254" s="6" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="H254" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I254" s="8" t="s">
         <v>285</v>
@@ -11877,7 +11892,7 @@
         <v>192</v>
       </c>
       <c r="G256" s="6" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="H256" s="8" t="s">
         <v>288</v>
@@ -11906,7 +11921,7 @@
         <v>192</v>
       </c>
       <c r="G257" s="6" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H257" s="8" t="s">
         <v>295</v>
@@ -11938,7 +11953,7 @@
         <v>192</v>
       </c>
       <c r="H258" s="6" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="I258" s="8" t="s">
         <v>192</v>
@@ -11964,13 +11979,13 @@
         <v>192</v>
       </c>
       <c r="G259" s="6" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="H259" s="8" t="s">
-        <v>118</v>
+        <v>459</v>
       </c>
       <c r="I259" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
@@ -11981,25 +11996,25 @@
         <v>276</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D260" s="8">
         <v>1</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F260" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G260" s="8" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="H260" s="6" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="I260" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
@@ -12010,22 +12025,22 @@
         <v>276</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D261" s="8">
         <v>2</v>
       </c>
       <c r="E261" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F261" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G261" s="6" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="H261" s="8" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="I261" s="8" t="s">
         <v>192</v>
@@ -12039,7 +12054,7 @@
         <v>276</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="D262" s="8">
         <v>1</v>
@@ -12054,7 +12069,7 @@
         <v>192</v>
       </c>
       <c r="H262" s="6" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="I262" s="8" t="s">
         <v>192</v>
@@ -12068,7 +12083,7 @@
         <v>276</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="D263" s="8">
         <v>2</v>
@@ -12077,13 +12092,13 @@
         <v>217</v>
       </c>
       <c r="F263" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G263" s="8" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="H263" s="8" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="I263" s="8" t="s">
         <v>192</v>
@@ -12097,25 +12112,25 @@
         <v>276</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="D264" s="8">
         <v>3</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F264" s="6" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="G264" s="6" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="H264" s="8" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="I264" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
@@ -12123,25 +12138,25 @@
         <v>133</v>
       </c>
       <c r="B265" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D265" s="8">
         <v>1</v>
       </c>
       <c r="E265" s="8" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="F265" s="8" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="G265" s="8" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="H265" s="8" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="I265" s="8" t="s">
         <v>192</v>
@@ -12152,25 +12167,25 @@
         <v>133</v>
       </c>
       <c r="B266" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C266" s="8" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D266" s="8">
         <v>2</v>
       </c>
       <c r="E266" s="8" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F266" s="8" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="G266" s="8" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="H266" s="8" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="I266" s="8" t="s">
         <v>192</v>
@@ -12181,25 +12196,25 @@
         <v>133</v>
       </c>
       <c r="B267" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C267" s="8" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D267" s="8">
         <v>3</v>
       </c>
       <c r="E267" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F267" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G267" s="6" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="H267" s="8" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="I267" s="8" t="s">
         <v>192</v>
@@ -12210,25 +12225,25 @@
         <v>133</v>
       </c>
       <c r="B268" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D268" s="8">
         <v>1</v>
       </c>
       <c r="E268" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F268" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G268" s="8" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="H268" s="8" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="I268" s="8" t="s">
         <v>192</v>
@@ -12239,16 +12254,16 @@
         <v>133</v>
       </c>
       <c r="B269" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D269" s="8">
         <v>2</v>
       </c>
       <c r="E269" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F269" s="8" t="s">
         <v>192</v>
@@ -12257,7 +12272,7 @@
         <v>192</v>
       </c>
       <c r="H269" s="6" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="I269" s="8" t="s">
         <v>192</v>
@@ -12268,16 +12283,16 @@
         <v>133</v>
       </c>
       <c r="B270" s="8" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="D270" s="8">
         <v>3</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F270" s="8" t="s">
         <v>192</v>
@@ -12286,7 +12301,7 @@
         <v>192</v>
       </c>
       <c r="H270" s="8" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="I270" s="8" t="s">
         <v>192</v>
@@ -12306,7 +12321,7 @@
         <v>1</v>
       </c>
       <c r="E271" s="8" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="F271" s="8" t="s">
         <v>192</v>
@@ -12315,7 +12330,7 @@
         <v>192</v>
       </c>
       <c r="H271" s="6" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I271" s="8" t="s">
         <v>192</v>
@@ -12341,13 +12356,13 @@
         <v>265</v>
       </c>
       <c r="G272" s="8" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="H272" s="8" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="I272" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
@@ -12373,10 +12388,10 @@
         <v>192</v>
       </c>
       <c r="H273" s="8" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="I273" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
@@ -12393,7 +12408,7 @@
         <v>4</v>
       </c>
       <c r="E274" s="8" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="F274" s="8" t="s">
         <v>192</v>
@@ -12402,7 +12417,7 @@
         <v>192</v>
       </c>
       <c r="H274" s="6" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="I274" s="8" t="s">
         <v>192</v>
@@ -12457,10 +12472,10 @@
         <v>192</v>
       </c>
       <c r="G276" s="6" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="H276" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I276" s="8" t="s">
         <v>285</v>
@@ -12515,7 +12530,7 @@
         <v>192</v>
       </c>
       <c r="G278" s="6" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="H278" s="8" t="s">
         <v>288</v>
@@ -12544,7 +12559,7 @@
         <v>192</v>
       </c>
       <c r="G279" s="6" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H279" s="8" t="s">
         <v>295</v>
@@ -12576,7 +12591,7 @@
         <v>192</v>
       </c>
       <c r="H280" s="6" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="I280" s="8" t="s">
         <v>192</v>
@@ -12602,13 +12617,13 @@
         <v>192</v>
       </c>
       <c r="G281" s="6" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="H281" s="8" t="s">
-        <v>118</v>
+        <v>459</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
@@ -12619,25 +12634,25 @@
         <v>276</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D282" s="8">
         <v>1</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F282" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G282" s="8" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="H282" s="6" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
@@ -12648,22 +12663,22 @@
         <v>276</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D283" s="8">
         <v>2</v>
       </c>
       <c r="E283" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F283" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G283" s="6" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="H283" s="8" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="I283" s="8" t="s">
         <v>192</v>
@@ -12677,7 +12692,7 @@
         <v>276</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D284" s="8">
         <v>1</v>
@@ -12692,7 +12707,7 @@
         <v>192</v>
       </c>
       <c r="H284" s="6" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="I284" s="8" t="s">
         <v>192</v>
@@ -12706,7 +12721,7 @@
         <v>276</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D285" s="8">
         <v>2</v>
@@ -12715,13 +12730,13 @@
         <v>217</v>
       </c>
       <c r="F285" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G285" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="H285" s="8" t="s">
         <v>578</v>
-      </c>
-      <c r="H285" s="8" t="s">
-        <v>573</v>
       </c>
       <c r="I285" s="8" t="s">
         <v>192</v>
@@ -12735,25 +12750,25 @@
         <v>276</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D286" s="8">
         <v>3</v>
       </c>
       <c r="E286" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F286" s="6" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="G286" s="6" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="H286" s="8" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="I286" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
@@ -12761,28 +12776,28 @@
         <v>136</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D287" s="8">
         <v>1</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="F287" s="8" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="G287" s="8" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="H287" s="8" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="I287" s="8" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
@@ -12790,25 +12805,25 @@
         <v>136</v>
       </c>
       <c r="B288" s="8" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C288" s="8" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D288" s="8">
         <v>2</v>
       </c>
       <c r="E288" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F288" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G288" s="6" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="H288" s="8" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="I288" s="8" t="s">
         <v>192</v>
@@ -12819,25 +12834,25 @@
         <v>136</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D289" s="8">
         <v>1</v>
       </c>
       <c r="E289" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F289" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G289" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="H289" s="8" t="s">
         <v>578</v>
-      </c>
-      <c r="H289" s="8" t="s">
-        <v>573</v>
       </c>
       <c r="I289" s="8" t="s">
         <v>192</v>
@@ -12848,16 +12863,16 @@
         <v>136</v>
       </c>
       <c r="B290" s="8" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D290" s="8">
         <v>2</v>
       </c>
       <c r="E290" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F290" s="8" t="s">
         <v>192</v>
@@ -12866,7 +12881,7 @@
         <v>192</v>
       </c>
       <c r="H290" s="6" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="I290" s="8" t="s">
         <v>192</v>
@@ -12877,16 +12892,16 @@
         <v>136</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="D291" s="8">
         <v>3</v>
       </c>
       <c r="E291" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F291" s="8" t="s">
         <v>192</v>
@@ -12895,7 +12910,7 @@
         <v>192</v>
       </c>
       <c r="H291" s="8" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="I291" s="8" t="s">
         <v>192</v>
@@ -12915,7 +12930,7 @@
         <v>1</v>
       </c>
       <c r="E292" s="8" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F292" s="8" t="s">
         <v>192</v>
@@ -12924,7 +12939,7 @@
         <v>192</v>
       </c>
       <c r="H292" s="6" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="I292" s="8" t="s">
         <v>192</v>
@@ -12950,13 +12965,13 @@
         <v>265</v>
       </c>
       <c r="G293" s="8" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="H293" s="8" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="I293" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
@@ -12982,10 +12997,10 @@
         <v>192</v>
       </c>
       <c r="H294" s="8" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="I294" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
@@ -13037,10 +13052,10 @@
         <v>192</v>
       </c>
       <c r="G296" s="6" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="H296" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I296" s="8" t="s">
         <v>285</v>
@@ -13124,7 +13139,7 @@
         <v>192</v>
       </c>
       <c r="G299" s="6" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="H299" s="8" t="s">
         <v>295</v>
@@ -13156,7 +13171,7 @@
         <v>192</v>
       </c>
       <c r="H300" s="6" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="I300" s="8" t="s">
         <v>192</v>
@@ -13182,13 +13197,13 @@
         <v>192</v>
       </c>
       <c r="G301" s="8" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="H301" s="8" t="s">
-        <v>113</v>
+        <v>447</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
@@ -13199,25 +13214,25 @@
         <v>276</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="D302" s="8">
         <v>1</v>
       </c>
       <c r="E302" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F302" s="8" t="s">
         <v>192</v>
       </c>
       <c r="G302" s="8" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="H302" s="6" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="I302" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
@@ -13228,22 +13243,22 @@
         <v>276</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="D303" s="8">
         <v>2</v>
       </c>
       <c r="E303" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F303" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G303" s="6" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="H303" s="8" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="I303" s="8" t="s">
         <v>192</v>
@@ -13257,7 +13272,7 @@
         <v>276</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D304" s="8">
         <v>1</v>
@@ -13272,7 +13287,7 @@
         <v>192</v>
       </c>
       <c r="H304" s="6" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="I304" s="8" t="s">
         <v>192</v>
@@ -13286,7 +13301,7 @@
         <v>276</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D305" s="8">
         <v>2</v>
@@ -13298,10 +13313,10 @@
         <v>198</v>
       </c>
       <c r="G305" s="8" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="H305" s="8" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="I305" s="8" t="s">
         <v>192</v>
@@ -13315,25 +13330,25 @@
         <v>276</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="D306" s="8">
         <v>3</v>
       </c>
       <c r="E306" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F306" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G306" s="6" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="H306" s="8" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="I306" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
@@ -13341,25 +13356,25 @@
         <v>139</v>
       </c>
       <c r="B307" s="8" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C307" s="8" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="D307" s="8">
         <v>1</v>
       </c>
       <c r="E307" s="8" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F307" s="8" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="G307" s="8" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="H307" s="8" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="I307" s="8" t="s">
         <v>192</v>
@@ -13370,25 +13385,25 @@
         <v>139</v>
       </c>
       <c r="B308" s="8" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C308" s="8" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="D308" s="8">
         <v>2</v>
       </c>
       <c r="E308" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F308" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G308" s="6" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="H308" s="6" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="I308" s="8" t="s">
         <v>192</v>
@@ -13399,25 +13414,25 @@
         <v>139</v>
       </c>
       <c r="B309" s="8" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D309" s="8">
         <v>1</v>
       </c>
       <c r="E309" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F309" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G309" s="8" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="H309" s="8" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="I309" s="8" t="s">
         <v>192</v>
@@ -13428,16 +13443,16 @@
         <v>139</v>
       </c>
       <c r="B310" s="8" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D310" s="8">
         <v>2</v>
       </c>
       <c r="E310" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F310" s="8" t="s">
         <v>192</v>
@@ -13446,7 +13461,7 @@
         <v>192</v>
       </c>
       <c r="H310" s="6" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="I310" s="8" t="s">
         <v>192</v>
@@ -13457,16 +13472,16 @@
         <v>139</v>
       </c>
       <c r="B311" s="8" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="D311" s="8">
         <v>3</v>
       </c>
       <c r="E311" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F311" s="8" t="s">
         <v>192</v>
@@ -13475,7 +13490,7 @@
         <v>192</v>
       </c>
       <c r="H311" s="8" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="I311" s="8" t="s">
         <v>192</v>
@@ -13507,50 +13522,50 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>

--- a/examples/reportes/memoria.xlsx
+++ b/examples/reportes/memoria.xlsx
@@ -521,7 +521,7 @@
     <t>CG-01</t>
   </si>
   <si>
-    <t>TG — 480 V · 3F4H</t>
+    <t>TG — 480/277 V · 3F4H</t>
   </si>
   <si>
     <t>Alimenta a</t>
@@ -581,7 +581,7 @@
     <t>{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","_margin":null,"_inlines":[],"_minWidth":53.4638671875,"_maxWidth":269.650390625,"listMarker":{"canvas":[{"x":41.166666666666664,"y":268.3580729166667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":264.197265625,"verticalRatio":0.41511097989341084,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":264.197265625,"verticalRatio":0.41511097989341084,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":39,"stack":false},"pageBreakCalculated":true}</t>
   </si>
   <si>
-    <t>CCM-1 — 480 V · 3F4H</t>
+    <t>CCM-1 — 480/277 V · 3F4H</t>
   </si>
   <si>
     <t>{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","_margin":null,"_inlines":[],"_minWidth":35.87158203125,"_maxWidth":225.96875,"listMarker":{"canvas":[{"x":41.166666666666664,"y":443.8424479166667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":439.681640625,"verticalRatio":0.7551969779554264,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Potencia demandada (con el factor de demanda capturado en cada carga).","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":439.681640625,"verticalRatio":0.7551969779554264,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":39,"stack":false},"pageBreakCalculated":true}</t>
@@ -593,7 +593,7 @@
     <t>{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","_margin":null,"_inlines":[],"_minWidth":53.4638671875,"_maxWidth":269.650390625,"listMarker":{"canvas":[{"x":41.166666666666664,"y":462.7096354166667,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":458.548828125,"verticalRatio":0.7917612948158915,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Transformadores, variadores y UPS se reparten equilibrados en sus tres fases de entrada.","startPosition":{"pageNumber":4,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":458.548828125,"verticalRatio":0.7917612948158915,"horizontalRatio":0.010287509875351123},"pageNumbers":[4],"pages":39,"stack":false},"pageBreakCalculated":true}</t>
   </si>
   <si>
-    <t>TAB-B — 480 V · 3F4H</t>
+    <t>TAB-B — 480/277 V · 3F4H</t>
   </si>
   <si>
     <t>A</t>
@@ -605,7 +605,7 @@
     <t>{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","_margin":null,"_inlines":[],"_minWidth":35.31787109375,"_maxWidth":412.8359375,"listMarker":{"canvas":[{"x":41.166666666666664,"y":145.73893229166666,"r1":1.1666666666666667,"r2":1.1666666666666667,"type":"ellipse","color":"#666"}],"_maxWidth":7.32470703125,"_minWidth":7.32470703125,"_maxHeight":9.43359375,"_minHeight":9.43359375},"positions":[{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":141.578125,"verticalRatio":0.17747698643410853,"horizontalRatio":0.010287509875351123}],"__height":9.43359375,"nodeInfo":{"text":"Desbalance = (F_máx − F_mín) / F_máx · 100; límite del proyecto 5 % (criterio de práctica común; la norma de instalación no fija un valor).","startPosition":{"pageNumber":5,"pageOrientation":"landscape","pageInnerHeight":516,"pageInnerWidth":712,"left":47.32470703125,"top":141.578125,"verticalRatio":0.17747698643410853,"horizontalRatio":0.010287509875351123},"pageNumbers":[5],"pages":39,"stack":false},"pageBreakCalculated":true}</t>
   </si>
   <si>
-    <t>TAB-A — 220 V · 3F4H</t>
+    <t>TAB-A — 220/127 V · 3F4H</t>
   </si>
   <si>
     <t>B</t>
